--- a/library/pdr/ai-mini-drama/ios/cases.xlsx
+++ b/library/pdr/ai-mini-drama/ios/cases.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3428" uniqueCount="2109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3452" uniqueCount="2126">
   <si>
     <t>ID</t>
   </si>
@@ -3227,6 +3227,57 @@
     <t>Figma flow arrow 2820-116880</t>
   </si>
   <si>
+    <t>TC-428</t>
+  </si>
+  <si>
+    <t>Finished video with two failed clips (Pink › Inject failure status on two scenes, then the switch Off; record the switch); Fix scenes open</t>
+  </si>
+  <si>
+    <t>Edit failed clip A › Done › Regenerate Clip; while clip A regenerates, Edit failed clip B, change its description, tap Done; read clip B's 「Regenerate Clip」 and the credit pill, then tap 「Regenerate Clip」</t>
+  </si>
+  <si>
+    <t>While clip A regenerates, clip B's 「Regenerate Clip」: the button is drawn at about 40% opacity but still responds (not disabled); tapping it shows the toast 「Another clip is regenerating. Try again when it's done.」; nothing is sent (that clip shows no generating state), no credits are charged (credit pill and Mine › Credits › Details unchanged) and its edited description is kept</t>
+  </si>
+  <si>
+    <t>R-466, R-134</t>
+  </si>
+  <si>
+    <t>PM §13.25 (Figma 4784:70878, 10/29 update, Figma only; board-notes 「PM — 10/29 Regenerate Clip one at a time」).</t>
+  </si>
+  <si>
+    <t>TC-429</t>
+  </si>
+  <si>
+    <t>Clip A regenerating and clip B's edited description kept after the toast (TC-428)</t>
+  </si>
+  <si>
+    <t>Wait until clip A's regeneration ends, then tap clip B's 「Regenerate Clip」; repeat once with clip A's regeneration failing (Pink › Inject failure status on clip A's scene; record the switch)</t>
+  </si>
+  <si>
+    <t>As soon as clip A ends, succeeded or failed, clip B's 「Regenerate Clip」 is back at full opacity; tapping it starts clip B's regeneration with the edited description and charges it once</t>
+  </si>
+  <si>
+    <t>R-466</t>
+  </si>
+  <si>
+    <t>TC-430</t>
+  </si>
+  <si>
+    <t>Finished video; one scene video regenerating, started from its scene editor (as TC-144)</t>
+  </si>
+  <si>
+    <t>Open another scene's editor (scene edit page), change its description, then tap its regenerate button</t>
+  </si>
+  <si>
+    <t>The other scene's regenerate button: the button is drawn at about 40% opacity but still responds (not disabled); tapping it shows the toast 「Another clip is regenerating. Try again when it's done.」; nothing is sent (that clip shows no generating state), no credits are charged (credit pill and Mine › Credits › Details unchanged) and its edited description is kept</t>
+  </si>
+  <si>
+    <t>R-466, R-081</t>
+  </si>
+  <si>
+    <t>PM §13.25 (Figma 4784:70878, 10/29 update, Figma only; board-notes 「PM — 10/29 Regenerate Clip one at a time」). The rule covers every single-clip regenerate entry (Fix Scene › Edit and the scene edit page).</t>
+  </si>
+  <si>
     <t>TC-150</t>
   </si>
   <si>
@@ -6308,19 +6359,19 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11</t>
+    <t>12</t>
   </si>
   <si>
     <t>Approved</t>
   </si>
   <si>
-    <t>2026-10-29T07:32:43.681Z</t>
+    <t>2026-10-30T09:24:55.782Z</t>
   </si>
   <si>
     <t>Cases</t>
   </si>
   <si>
-    <t>425</t>
+    <t>428</t>
   </si>
   <si>
     <t>Spec set SHA-256</t>
@@ -6735,7 +6786,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H426"/>
+  <dimension ref="A1:H429"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -11989,7 +12040,7 @@
         <v>1074</v>
       </c>
       <c r="F202" s="3" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="G202" s="3" t="s">
         <v>1075</v>
@@ -12003,7 +12054,7 @@
         <v>1077</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>727</v>
+        <v>671</v>
       </c>
       <c r="C203" s="3" t="s">
         <v>1078</v>
@@ -12021,148 +12072,148 @@
         <v>1081</v>
       </c>
       <c r="H203" s="3" t="s">
-        <v>1082</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204" s="3" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B204" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="C204" s="3" t="s">
         <v>1083</v>
       </c>
-      <c r="B204" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="C204" s="3" t="s">
+      <c r="D204" s="3" t="s">
         <v>1084</v>
       </c>
-      <c r="D204" s="3" t="s">
+      <c r="E204" s="3" t="s">
         <v>1085</v>
       </c>
-      <c r="E204" s="3" t="s">
+      <c r="F204" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G204" s="3" t="s">
         <v>1086</v>
       </c>
-      <c r="F204" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G204" s="3" t="s">
+      <c r="H204" s="3" t="s">
         <v>1087</v>
-      </c>
-      <c r="H204" s="3" t="s">
-        <v>1088</v>
       </c>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205" s="3" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B205" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="C205" s="3" t="s">
         <v>1089</v>
       </c>
-      <c r="B205" s="3" t="s">
+      <c r="D205" s="3" t="s">
         <v>1090</v>
       </c>
-      <c r="C205" s="3" t="s">
+      <c r="E205" s="3" t="s">
         <v>1091</v>
       </c>
-      <c r="D205" s="3" t="s">
+      <c r="F205" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G205" s="3" t="s">
         <v>1092</v>
       </c>
-      <c r="E205" s="3" t="s">
+      <c r="H205" s="3" t="s">
         <v>1093</v>
-      </c>
-      <c r="F205" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G205" s="3" t="s">
-        <v>1094</v>
-      </c>
-      <c r="H205" s="3" t="s">
-        <v>1095</v>
       </c>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A206" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B206" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="C206" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="D206" s="3" t="s">
         <v>1096</v>
       </c>
-      <c r="B206" s="3" t="s">
-        <v>1090</v>
-      </c>
-      <c r="C206" s="3" t="s">
+      <c r="E206" s="3" t="s">
         <v>1097</v>
       </c>
-      <c r="D206" s="3" t="s">
-        <v>1092</v>
-      </c>
-      <c r="E206" s="3" t="s">
-        <v>1093</v>
-      </c>
       <c r="F206" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G206" s="3" t="s">
-        <v>1094</v>
+        <v>1098</v>
       </c>
       <c r="H206" s="3" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A207" s="3" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>1090</v>
+        <v>198</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>1092</v>
+        <v>1102</v>
       </c>
       <c r="E207" s="3" t="s">
-        <v>1093</v>
+        <v>1103</v>
       </c>
       <c r="F207" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G207" s="3" t="s">
-        <v>1094</v>
+        <v>1104</v>
       </c>
       <c r="H207" s="3" t="s">
-        <v>1101</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208" s="3" t="s">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>1090</v>
+        <v>1107</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>1103</v>
+        <v>1108</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>1104</v>
+        <v>1109</v>
       </c>
       <c r="E208" s="3" t="s">
-        <v>1105</v>
+        <v>1110</v>
       </c>
       <c r="F208" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G208" s="3" t="s">
-        <v>544</v>
+        <v>1111</v>
       </c>
       <c r="H208" s="3" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" s="3" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B209" s="3" t="s">
         <v>1107</v>
       </c>
-      <c r="B209" s="3" t="s">
-        <v>1090</v>
-      </c>
       <c r="C209" s="3" t="s">
-        <v>1108</v>
+        <v>1114</v>
       </c>
       <c r="D209" s="3" t="s">
         <v>1109</v>
@@ -12174,111 +12225,111 @@
         <v>26</v>
       </c>
       <c r="G209" s="3" t="s">
-        <v>544</v>
+        <v>1111</v>
       </c>
       <c r="H209" s="3" t="s">
-        <v>1106</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210" s="3" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B210" s="3" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C210" s="3" t="s">
+        <v>1117</v>
+      </c>
+      <c r="D210" s="3" t="s">
+        <v>1109</v>
+      </c>
+      <c r="E210" s="3" t="s">
+        <v>1110</v>
+      </c>
+      <c r="F210" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G210" s="3" t="s">
         <v>1111</v>
       </c>
-      <c r="B210" s="3" t="s">
-        <v>1090</v>
-      </c>
-      <c r="C210" s="3" t="s">
-        <v>1112</v>
-      </c>
-      <c r="D210" s="3" t="s">
-        <v>1113</v>
-      </c>
-      <c r="E210" s="3" t="s">
-        <v>1114</v>
-      </c>
-      <c r="F210" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G210" s="3" t="s">
-        <v>1115</v>
-      </c>
       <c r="H210" s="3" t="s">
-        <v>15</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211" s="3" t="s">
-        <v>1116</v>
+        <v>1119</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>1090</v>
+        <v>1107</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>1113</v>
+        <v>1121</v>
       </c>
       <c r="E211" s="3" t="s">
-        <v>1114</v>
+        <v>1122</v>
       </c>
       <c r="F211" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G211" s="3" t="s">
-        <v>1115</v>
+        <v>544</v>
       </c>
       <c r="H211" s="3" t="s">
-        <v>15</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212" s="3" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>1090</v>
+        <v>1107</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>1119</v>
+        <v>1125</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>1113</v>
+        <v>1126</v>
       </c>
       <c r="E212" s="3" t="s">
-        <v>1114</v>
+        <v>1127</v>
       </c>
       <c r="F212" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G212" s="3" t="s">
-        <v>1115</v>
+        <v>544</v>
       </c>
       <c r="H212" s="3" t="s">
-        <v>15</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213" s="3" t="s">
-        <v>1120</v>
+        <v>1128</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>1090</v>
+        <v>1107</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>1121</v>
+        <v>1129</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>1113</v>
+        <v>1130</v>
       </c>
       <c r="E213" s="3" t="s">
-        <v>1114</v>
+        <v>1131</v>
       </c>
       <c r="F213" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G213" s="3" t="s">
-        <v>1115</v>
+        <v>1132</v>
       </c>
       <c r="H213" s="3" t="s">
         <v>15</v>
@@ -12286,25 +12337,25 @@
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" s="3" t="s">
-        <v>1122</v>
+        <v>1133</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>1090</v>
+        <v>1107</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>1123</v>
+        <v>1134</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>1113</v>
+        <v>1130</v>
       </c>
       <c r="E214" s="3" t="s">
-        <v>1114</v>
+        <v>1131</v>
       </c>
       <c r="F214" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G214" s="3" t="s">
-        <v>1115</v>
+        <v>1132</v>
       </c>
       <c r="H214" s="3" t="s">
         <v>15</v>
@@ -12312,25 +12363,25 @@
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A215" s="3" t="s">
-        <v>1124</v>
+        <v>1135</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>1090</v>
+        <v>1107</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>1125</v>
+        <v>1136</v>
       </c>
       <c r="D215" s="3" t="s">
-        <v>1113</v>
+        <v>1130</v>
       </c>
       <c r="E215" s="3" t="s">
-        <v>1114</v>
+        <v>1131</v>
       </c>
       <c r="F215" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G215" s="3" t="s">
-        <v>1115</v>
+        <v>1132</v>
       </c>
       <c r="H215" s="3" t="s">
         <v>15</v>
@@ -12338,25 +12389,25 @@
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A216" s="3" t="s">
-        <v>1126</v>
+        <v>1137</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>1090</v>
+        <v>1107</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>1127</v>
+        <v>1138</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>1113</v>
+        <v>1130</v>
       </c>
       <c r="E216" s="3" t="s">
-        <v>1114</v>
+        <v>1131</v>
       </c>
       <c r="F216" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G216" s="3" t="s">
-        <v>1115</v>
+        <v>1132</v>
       </c>
       <c r="H216" s="3" t="s">
         <v>15</v>
@@ -12364,25 +12415,25 @@
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A217" s="3" t="s">
-        <v>1128</v>
+        <v>1139</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>1090</v>
+        <v>1107</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>1129</v>
+        <v>1140</v>
       </c>
       <c r="D217" s="3" t="s">
-        <v>1113</v>
+        <v>1130</v>
       </c>
       <c r="E217" s="3" t="s">
-        <v>1114</v>
+        <v>1131</v>
       </c>
       <c r="F217" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G217" s="3" t="s">
-        <v>1115</v>
+        <v>1132</v>
       </c>
       <c r="H217" s="3" t="s">
         <v>15</v>
@@ -12390,25 +12441,25 @@
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218" s="3" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B218" s="3" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C218" s="3" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D218" s="3" t="s">
         <v>1130</v>
       </c>
-      <c r="B218" s="3" t="s">
-        <v>1090</v>
-      </c>
-      <c r="C218" s="3" t="s">
+      <c r="E218" s="3" t="s">
         <v>1131</v>
       </c>
-      <c r="D218" s="3" t="s">
-        <v>1113</v>
-      </c>
-      <c r="E218" s="3" t="s">
-        <v>1114</v>
-      </c>
       <c r="F218" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G218" s="3" t="s">
-        <v>1115</v>
+        <v>1132</v>
       </c>
       <c r="H218" s="3" t="s">
         <v>15</v>
@@ -12416,25 +12467,25 @@
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" s="3" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B219" s="3" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C219" s="3" t="s">
+        <v>1144</v>
+      </c>
+      <c r="D219" s="3" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E219" s="3" t="s">
+        <v>1131</v>
+      </c>
+      <c r="F219" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G219" s="3" t="s">
         <v>1132</v>
-      </c>
-      <c r="B219" s="3" t="s">
-        <v>1090</v>
-      </c>
-      <c r="C219" s="3" t="s">
-        <v>1133</v>
-      </c>
-      <c r="D219" s="3" t="s">
-        <v>1113</v>
-      </c>
-      <c r="E219" s="3" t="s">
-        <v>1114</v>
-      </c>
-      <c r="F219" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G219" s="3" t="s">
-        <v>1115</v>
       </c>
       <c r="H219" s="3" t="s">
         <v>15</v>
@@ -12442,25 +12493,25 @@
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A220" s="3" t="s">
-        <v>1134</v>
+        <v>1145</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>1090</v>
+        <v>1107</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>1135</v>
+        <v>1146</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>1113</v>
+        <v>1130</v>
       </c>
       <c r="E220" s="3" t="s">
-        <v>1114</v>
+        <v>1131</v>
       </c>
       <c r="F220" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G220" s="3" t="s">
-        <v>1115</v>
+        <v>1132</v>
       </c>
       <c r="H220" s="3" t="s">
         <v>15</v>
@@ -12468,181 +12519,181 @@
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221" s="3" t="s">
-        <v>1136</v>
+        <v>1147</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>1137</v>
+        <v>1107</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>1138</v>
+        <v>1148</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>1139</v>
+        <v>1130</v>
       </c>
       <c r="E221" s="3" t="s">
-        <v>1140</v>
+        <v>1131</v>
       </c>
       <c r="F221" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G221" s="3" t="s">
-        <v>1141</v>
+        <v>1132</v>
       </c>
       <c r="H221" s="3" t="s">
-        <v>1142</v>
+        <v>15</v>
       </c>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A222" s="3" t="s">
-        <v>1143</v>
+        <v>1149</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>1137</v>
+        <v>1107</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>1144</v>
+        <v>1150</v>
       </c>
       <c r="D222" s="3" t="s">
-        <v>1139</v>
+        <v>1130</v>
       </c>
       <c r="E222" s="3" t="s">
-        <v>1140</v>
+        <v>1131</v>
       </c>
       <c r="F222" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G222" s="3" t="s">
-        <v>1141</v>
+        <v>1132</v>
       </c>
       <c r="H222" s="3" t="s">
-        <v>1145</v>
+        <v>15</v>
       </c>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A223" s="3" t="s">
-        <v>1146</v>
+        <v>1151</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>1137</v>
+        <v>1107</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>1147</v>
+        <v>1152</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>1139</v>
+        <v>1130</v>
       </c>
       <c r="E223" s="3" t="s">
-        <v>1140</v>
+        <v>1131</v>
       </c>
       <c r="F223" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G223" s="3" t="s">
-        <v>1141</v>
+        <v>1132</v>
       </c>
       <c r="H223" s="3" t="s">
-        <v>1148</v>
+        <v>15</v>
       </c>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A224" s="3" t="s">
-        <v>1149</v>
+        <v>1153</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>1137</v>
+        <v>1154</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>1150</v>
+        <v>1155</v>
       </c>
       <c r="D224" s="3" t="s">
-        <v>1139</v>
+        <v>1156</v>
       </c>
       <c r="E224" s="3" t="s">
-        <v>1140</v>
+        <v>1157</v>
       </c>
       <c r="F224" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G224" s="3" t="s">
-        <v>1141</v>
+        <v>1158</v>
       </c>
       <c r="H224" s="3" t="s">
-        <v>1145</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A225" s="3" t="s">
-        <v>1151</v>
+        <v>1160</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>1137</v>
+        <v>1154</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>1152</v>
+        <v>1161</v>
       </c>
       <c r="D225" s="3" t="s">
-        <v>1139</v>
+        <v>1156</v>
       </c>
       <c r="E225" s="3" t="s">
-        <v>1140</v>
+        <v>1157</v>
       </c>
       <c r="F225" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G225" s="3" t="s">
-        <v>1141</v>
+        <v>1158</v>
       </c>
       <c r="H225" s="3" t="s">
-        <v>1153</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226" s="3" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B226" s="3" t="s">
         <v>1154</v>
       </c>
-      <c r="B226" s="3" t="s">
-        <v>1137</v>
-      </c>
       <c r="C226" s="3" t="s">
-        <v>1155</v>
+        <v>1164</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>1139</v>
+        <v>1156</v>
       </c>
       <c r="E226" s="3" t="s">
-        <v>1140</v>
+        <v>1157</v>
       </c>
       <c r="F226" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G226" s="3" t="s">
-        <v>1141</v>
+        <v>1158</v>
       </c>
       <c r="H226" s="3" t="s">
-        <v>1145</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A227" s="3" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B227" s="3" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C227" s="3" t="s">
+        <v>1167</v>
+      </c>
+      <c r="D227" s="3" t="s">
         <v>1156</v>
       </c>
-      <c r="B227" s="3" t="s">
+      <c r="E227" s="3" t="s">
         <v>1157</v>
       </c>
-      <c r="C227" s="3" t="s">
+      <c r="F227" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G227" s="3" t="s">
         <v>1158</v>
-      </c>
-      <c r="D227" s="3" t="s">
-        <v>1159</v>
-      </c>
-      <c r="E227" s="3" t="s">
-        <v>1160</v>
-      </c>
-      <c r="F227" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G227" s="3" t="s">
-        <v>1161</v>
       </c>
       <c r="H227" s="3" t="s">
         <v>1162</v>
@@ -12650,54 +12701,54 @@
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228" s="3" t="s">
-        <v>1163</v>
+        <v>1168</v>
       </c>
       <c r="B228" s="3" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C228" s="3" t="s">
+        <v>1169</v>
+      </c>
+      <c r="D228" s="3" t="s">
+        <v>1156</v>
+      </c>
+      <c r="E228" s="3" t="s">
         <v>1157</v>
       </c>
-      <c r="C228" s="3" t="s">
-        <v>1164</v>
-      </c>
-      <c r="D228" s="3" t="s">
-        <v>1165</v>
-      </c>
-      <c r="E228" s="3" t="s">
-        <v>1166</v>
-      </c>
       <c r="F228" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G228" s="3" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="H228" s="3" t="s">
-        <v>1167</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229" s="3" t="s">
-        <v>1168</v>
+        <v>1171</v>
       </c>
       <c r="B229" s="3" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C229" s="3" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D229" s="3" t="s">
+        <v>1156</v>
+      </c>
+      <c r="E229" s="3" t="s">
         <v>1157</v>
       </c>
-      <c r="C229" s="3" t="s">
-        <v>1169</v>
-      </c>
-      <c r="D229" s="3" t="s">
-        <v>1170</v>
-      </c>
-      <c r="E229" s="3" t="s">
-        <v>1171</v>
-      </c>
       <c r="F229" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G229" s="3" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="H229" s="3" t="s">
-        <v>1172</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.25">
@@ -12705,984 +12756,984 @@
         <v>1173</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="C230" s="3" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="E230" s="3" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="F230" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G230" s="3" t="s">
-        <v>1161</v>
+        <v>1178</v>
       </c>
       <c r="H230" s="3" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231" s="3" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B231" s="3" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C231" s="3" t="s">
+        <v>1181</v>
+      </c>
+      <c r="D231" s="3" t="s">
+        <v>1182</v>
+      </c>
+      <c r="E231" s="3" t="s">
+        <v>1183</v>
+      </c>
+      <c r="F231" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G231" s="3" t="s">
         <v>1178</v>
       </c>
-      <c r="B231" s="3" t="s">
-        <v>1157</v>
-      </c>
-      <c r="C231" s="3" t="s">
-        <v>1179</v>
-      </c>
-      <c r="D231" s="3" t="s">
-        <v>1180</v>
-      </c>
-      <c r="E231" s="3" t="s">
-        <v>1181</v>
-      </c>
-      <c r="F231" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G231" s="3" t="s">
-        <v>1161</v>
-      </c>
       <c r="H231" s="3" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A232" s="3" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="C232" s="3" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="D232" s="3" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="E232" s="3" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="F232" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G232" s="3" t="s">
-        <v>1161</v>
+        <v>1178</v>
       </c>
       <c r="H232" s="3" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A233" s="3" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="D233" s="3" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="E233" s="3" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="F233" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G233" s="3" t="s">
-        <v>1161</v>
+        <v>1178</v>
       </c>
       <c r="H233" s="3" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A234" s="3" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="D234" s="3" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="E234" s="3" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="F234" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G234" s="3" t="s">
-        <v>1161</v>
+        <v>1178</v>
       </c>
       <c r="H234" s="3" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A235" s="3" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="C235" s="3" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="D235" s="3" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="E235" s="3" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="F235" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G235" s="3" t="s">
-        <v>1161</v>
+        <v>1178</v>
       </c>
       <c r="H235" s="3" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A236" s="3" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="C236" s="3" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="E236" s="3" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="F236" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G236" s="3" t="s">
-        <v>1161</v>
+        <v>1178</v>
       </c>
       <c r="H236" s="3" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A237" s="3" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="C237" s="3" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="D237" s="3" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="E237" s="3" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="F237" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G237" s="3" t="s">
-        <v>1161</v>
+        <v>1178</v>
       </c>
       <c r="H237" s="3" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238" s="3" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="C238" s="3" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="D238" s="3" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
       <c r="E238" s="3" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="F238" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G238" s="3" t="s">
-        <v>1161</v>
+        <v>1178</v>
       </c>
       <c r="H238" s="3" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A239" s="3" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="C239" s="3" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="D239" s="3" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="E239" s="3" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="F239" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G239" s="3" t="s">
-        <v>1161</v>
+        <v>1178</v>
       </c>
       <c r="H239" s="3" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A240" s="3" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="C240" s="3" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="D240" s="3" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="E240" s="3" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="F240" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G240" s="3" t="s">
-        <v>1161</v>
+        <v>1178</v>
       </c>
       <c r="H240" s="3" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A241" s="3" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="C241" s="3" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="D241" s="3" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="E241" s="3" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="F241" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G241" s="3" t="s">
-        <v>1161</v>
+        <v>1178</v>
       </c>
       <c r="H241" s="3" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242" s="3" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="C242" s="3" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="D242" s="3" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="E242" s="3" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="F242" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G242" s="3" t="s">
-        <v>1161</v>
+        <v>1178</v>
       </c>
       <c r="H242" s="3" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A243" s="3" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="C243" s="3" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
       <c r="D243" s="3" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="E243" s="3" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="F243" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G243" s="3" t="s">
-        <v>1161</v>
+        <v>1178</v>
       </c>
       <c r="H243" s="3" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A244" s="3" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="C244" s="3" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="D244" s="3" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="E244" s="3" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="F244" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G244" s="3" t="s">
-        <v>1161</v>
+        <v>1178</v>
       </c>
       <c r="H244" s="3" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A245" s="3" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="C245" s="3" t="s">
-        <v>1249</v>
+        <v>1251</v>
       </c>
       <c r="D245" s="3" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="E245" s="3" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="F245" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G245" s="3" t="s">
-        <v>1161</v>
+        <v>1178</v>
       </c>
       <c r="H245" s="3" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A246" s="3" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="C246" s="3" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
       <c r="D246" s="3" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="E246" s="3" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="F246" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G246" s="3" t="s">
-        <v>1161</v>
+        <v>1178</v>
       </c>
       <c r="H246" s="3" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247" s="3" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="C247" s="3" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
       <c r="D247" s="3" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="E247" s="3" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="F247" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G247" s="3" t="s">
-        <v>1161</v>
+        <v>1178</v>
       </c>
       <c r="H247" s="3" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A248" s="3" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="B248" s="3" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="C248" s="3" t="s">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="D248" s="3" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="E248" s="3" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="F248" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G248" s="3" t="s">
-        <v>1161</v>
+        <v>1178</v>
       </c>
       <c r="H248" s="3" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A249" s="3" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="C249" s="3" t="s">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="D249" s="3" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="E249" s="3" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="F249" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G249" s="3" t="s">
-        <v>1161</v>
+        <v>1178</v>
       </c>
       <c r="H249" s="3" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A250" s="3" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="B250" s="3" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="C250" s="3" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="D250" s="3" t="s">
-        <v>1275</v>
+        <v>1277</v>
       </c>
       <c r="E250" s="3" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="F250" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G250" s="3" t="s">
-        <v>1161</v>
+        <v>1178</v>
       </c>
       <c r="H250" s="3" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A251" s="3" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="D251" s="3" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="E251" s="3" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="F251" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G251" s="3" t="s">
-        <v>1161</v>
+        <v>1178</v>
       </c>
       <c r="H251" s="3" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A252" s="3" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="B252" s="3" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="C252" s="3" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="D252" s="3" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
       <c r="E252" s="3" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="F252" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G252" s="3" t="s">
-        <v>1161</v>
+        <v>1178</v>
       </c>
       <c r="H252" s="3" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A253" s="3" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="C253" s="3" t="s">
-        <v>1289</v>
+        <v>1291</v>
       </c>
       <c r="D253" s="3" t="s">
-        <v>1290</v>
+        <v>1292</v>
       </c>
       <c r="E253" s="3" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="F253" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G253" s="3" t="s">
-        <v>1161</v>
+        <v>1178</v>
       </c>
       <c r="H253" s="3" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A254" s="3" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="B254" s="3" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="C254" s="3" t="s">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="D254" s="3" t="s">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="E254" s="3" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="F254" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G254" s="3" t="s">
-        <v>1161</v>
+        <v>1178</v>
       </c>
       <c r="H254" s="3" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A255" s="3" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="B255" s="3" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="C255" s="3" t="s">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="D255" s="3" t="s">
-        <v>1300</v>
+        <v>1302</v>
       </c>
       <c r="E255" s="3" t="s">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="F255" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G255" s="3" t="s">
-        <v>1161</v>
+        <v>1178</v>
       </c>
       <c r="H255" s="3" t="s">
-        <v>1302</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A256" s="3" t="s">
-        <v>1303</v>
+        <v>1305</v>
       </c>
       <c r="B256" s="3" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="C256" s="3" t="s">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="D256" s="3" t="s">
-        <v>1305</v>
+        <v>1307</v>
       </c>
       <c r="E256" s="3" t="s">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="F256" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G256" s="3" t="s">
-        <v>1161</v>
+        <v>1178</v>
       </c>
       <c r="H256" s="3" t="s">
-        <v>1307</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A257" s="3" t="s">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="C257" s="3" t="s">
-        <v>1309</v>
+        <v>1311</v>
       </c>
       <c r="D257" s="3" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="E257" s="3" t="s">
-        <v>1311</v>
+        <v>1313</v>
       </c>
       <c r="F257" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G257" s="3" t="s">
-        <v>1161</v>
+        <v>1178</v>
       </c>
       <c r="H257" s="3" t="s">
-        <v>1312</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A258" s="3" t="s">
-        <v>1313</v>
+        <v>1315</v>
       </c>
       <c r="B258" s="3" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="C258" s="3" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="D258" s="3" t="s">
-        <v>1315</v>
+        <v>1317</v>
       </c>
       <c r="E258" s="3" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
       <c r="F258" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G258" s="3" t="s">
-        <v>1161</v>
+        <v>1178</v>
       </c>
       <c r="H258" s="3" t="s">
-        <v>1317</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A259" s="3" t="s">
-        <v>1318</v>
+        <v>1320</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="C259" s="3" t="s">
-        <v>1319</v>
+        <v>1321</v>
       </c>
       <c r="D259" s="3" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
       <c r="E259" s="3" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="F259" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G259" s="3" t="s">
-        <v>1161</v>
+        <v>1178</v>
       </c>
       <c r="H259" s="3" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A260" s="3" t="s">
-        <v>1323</v>
+        <v>1325</v>
       </c>
       <c r="B260" s="3" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="C260" s="3" t="s">
-        <v>1324</v>
+        <v>1326</v>
       </c>
       <c r="D260" s="3" t="s">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="E260" s="3" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="F260" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G260" s="3" t="s">
-        <v>1161</v>
+        <v>1178</v>
       </c>
       <c r="H260" s="3" t="s">
-        <v>1327</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A261" s="3" t="s">
-        <v>1328</v>
+        <v>1330</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="C261" s="3" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="D261" s="3" t="s">
-        <v>1330</v>
+        <v>1332</v>
       </c>
       <c r="E261" s="3" t="s">
-        <v>1331</v>
+        <v>1333</v>
       </c>
       <c r="F261" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G261" s="3" t="s">
-        <v>1161</v>
+        <v>1178</v>
       </c>
       <c r="H261" s="3" t="s">
-        <v>1332</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="262" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A262" s="3" t="s">
-        <v>1333</v>
+        <v>1335</v>
       </c>
       <c r="B262" s="3" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="C262" s="3" t="s">
-        <v>1334</v>
+        <v>1336</v>
       </c>
       <c r="D262" s="3" t="s">
-        <v>1335</v>
+        <v>1337</v>
       </c>
       <c r="E262" s="3" t="s">
-        <v>1336</v>
+        <v>1338</v>
       </c>
       <c r="F262" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G262" s="3" t="s">
-        <v>1161</v>
+        <v>1178</v>
       </c>
       <c r="H262" s="3" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="263" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A263" s="3" t="s">
-        <v>1338</v>
+        <v>1340</v>
       </c>
       <c r="B263" s="3" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="C263" s="3" t="s">
-        <v>1339</v>
+        <v>1341</v>
       </c>
       <c r="D263" s="3" t="s">
-        <v>1340</v>
+        <v>1342</v>
       </c>
       <c r="E263" s="3" t="s">
-        <v>1341</v>
+        <v>1343</v>
       </c>
       <c r="F263" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G263" s="3" t="s">
-        <v>1161</v>
+        <v>1178</v>
       </c>
       <c r="H263" s="3" t="s">
-        <v>1342</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="264" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A264" s="3" t="s">
-        <v>1343</v>
+        <v>1345</v>
       </c>
       <c r="B264" s="3" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="C264" s="3" t="s">
-        <v>1344</v>
+        <v>1346</v>
       </c>
       <c r="D264" s="3" t="s">
-        <v>1345</v>
+        <v>1347</v>
       </c>
       <c r="E264" s="3" t="s">
-        <v>1346</v>
+        <v>1348</v>
       </c>
       <c r="F264" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G264" s="3" t="s">
-        <v>1161</v>
+        <v>1178</v>
       </c>
       <c r="H264" s="3" t="s">
-        <v>1347</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="265" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A265" s="3" t="s">
-        <v>1348</v>
+        <v>1350</v>
       </c>
       <c r="B265" s="3" t="s">
-        <v>1157</v>
+        <v>1174</v>
       </c>
       <c r="C265" s="3" t="s">
-        <v>1349</v>
+        <v>1351</v>
       </c>
       <c r="D265" s="3" t="s">
-        <v>1350</v>
+        <v>1352</v>
       </c>
       <c r="E265" s="3" t="s">
-        <v>1351</v>
+        <v>1353</v>
       </c>
       <c r="F265" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G265" s="3" t="s">
-        <v>1161</v>
+        <v>1178</v>
       </c>
       <c r="H265" s="3" t="s">
-        <v>1352</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="266" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A266" s="3" t="s">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="B266" s="3" t="s">
-        <v>198</v>
+        <v>1174</v>
       </c>
       <c r="C266" s="3" t="s">
-        <v>1354</v>
+        <v>1356</v>
       </c>
       <c r="D266" s="3" t="s">
-        <v>1355</v>
+        <v>1357</v>
       </c>
       <c r="E266" s="3" t="s">
-        <v>1356</v>
+        <v>1358</v>
       </c>
       <c r="F266" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G266" s="3" t="s">
-        <v>1357</v>
+        <v>1178</v>
       </c>
       <c r="H266" s="3" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="267" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A267" s="3" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="B267" s="3" t="s">
-        <v>198</v>
+        <v>1174</v>
       </c>
       <c r="C267" s="3" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="D267" s="3" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="E267" s="3" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="F267" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G267" s="3" t="s">
-        <v>1363</v>
+        <v>1178</v>
       </c>
       <c r="H267" s="3" t="s">
         <v>1364</v>
@@ -13693,7 +13744,7 @@
         <v>1365</v>
       </c>
       <c r="B268" s="3" t="s">
-        <v>198</v>
+        <v>1174</v>
       </c>
       <c r="C268" s="3" t="s">
         <v>1366</v>
@@ -13708,7 +13759,7 @@
         <v>26</v>
       </c>
       <c r="G268" s="3" t="s">
-        <v>1357</v>
+        <v>1178</v>
       </c>
       <c r="H268" s="3" t="s">
         <v>1369</v>
@@ -13734,189 +13785,189 @@
         <v>26</v>
       </c>
       <c r="G269" s="3" t="s">
-        <v>1357</v>
+        <v>1374</v>
       </c>
       <c r="H269" s="3" t="s">
-        <v>15</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="270" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A270" s="3" t="s">
-        <v>1374</v>
+        <v>1376</v>
       </c>
       <c r="B270" s="3" t="s">
         <v>198</v>
       </c>
       <c r="C270" s="3" t="s">
-        <v>1375</v>
+        <v>1377</v>
       </c>
       <c r="D270" s="3" t="s">
-        <v>1372</v>
+        <v>1378</v>
       </c>
       <c r="E270" s="3" t="s">
-        <v>1376</v>
+        <v>1379</v>
       </c>
       <c r="F270" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G270" s="3" t="s">
-        <v>1357</v>
+        <v>1380</v>
       </c>
       <c r="H270" s="3" t="s">
-        <v>1377</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A271" s="3" t="s">
-        <v>1378</v>
+        <v>1382</v>
       </c>
       <c r="B271" s="3" t="s">
         <v>198</v>
       </c>
       <c r="C271" s="3" t="s">
-        <v>1379</v>
+        <v>1383</v>
       </c>
       <c r="D271" s="3" t="s">
-        <v>1372</v>
+        <v>1384</v>
       </c>
       <c r="E271" s="3" t="s">
-        <v>1380</v>
+        <v>1385</v>
       </c>
       <c r="F271" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G271" s="3" t="s">
-        <v>1357</v>
+        <v>1374</v>
       </c>
       <c r="H271" s="3" t="s">
-        <v>1381</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="272" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A272" s="3" t="s">
-        <v>1382</v>
+        <v>1387</v>
       </c>
       <c r="B272" s="3" t="s">
         <v>198</v>
       </c>
       <c r="C272" s="3" t="s">
-        <v>1383</v>
+        <v>1388</v>
       </c>
       <c r="D272" s="3" t="s">
-        <v>1384</v>
+        <v>1389</v>
       </c>
       <c r="E272" s="3" t="s">
-        <v>1385</v>
+        <v>1390</v>
       </c>
       <c r="F272" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G272" s="3" t="s">
-        <v>1386</v>
+        <v>1374</v>
       </c>
       <c r="H272" s="3" t="s">
-        <v>1387</v>
+        <v>15</v>
       </c>
     </row>
     <row r="273" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A273" s="3" t="s">
-        <v>1388</v>
+        <v>1391</v>
       </c>
       <c r="B273" s="3" t="s">
         <v>198</v>
       </c>
       <c r="C273" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="D273" s="3" t="s">
         <v>1389</v>
       </c>
-      <c r="D273" s="3" t="s">
-        <v>1384</v>
-      </c>
       <c r="E273" s="3" t="s">
-        <v>1390</v>
+        <v>1393</v>
       </c>
       <c r="F273" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G273" s="3" t="s">
-        <v>1386</v>
+        <v>1374</v>
       </c>
       <c r="H273" s="3" t="s">
-        <v>15</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="274" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A274" s="3" t="s">
-        <v>1391</v>
+        <v>1395</v>
       </c>
       <c r="B274" s="3" t="s">
         <v>198</v>
       </c>
       <c r="C274" s="3" t="s">
-        <v>1392</v>
+        <v>1396</v>
       </c>
       <c r="D274" s="3" t="s">
-        <v>1384</v>
+        <v>1389</v>
       </c>
       <c r="E274" s="3" t="s">
-        <v>1393</v>
+        <v>1397</v>
       </c>
       <c r="F274" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G274" s="3" t="s">
-        <v>1386</v>
+        <v>1374</v>
       </c>
       <c r="H274" s="3" t="s">
-        <v>15</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="275" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A275" s="3" t="s">
-        <v>1394</v>
+        <v>1399</v>
       </c>
       <c r="B275" s="3" t="s">
         <v>198</v>
       </c>
       <c r="C275" s="3" t="s">
-        <v>1395</v>
+        <v>1400</v>
       </c>
       <c r="D275" s="3" t="s">
-        <v>1396</v>
+        <v>1401</v>
       </c>
       <c r="E275" s="3" t="s">
-        <v>1397</v>
+        <v>1402</v>
       </c>
       <c r="F275" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G275" s="3" t="s">
-        <v>1398</v>
+        <v>1403</v>
       </c>
       <c r="H275" s="3" t="s">
-        <v>15</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="276" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A276" s="3" t="s">
-        <v>1399</v>
+        <v>1405</v>
       </c>
       <c r="B276" s="3" t="s">
         <v>198</v>
       </c>
       <c r="C276" s="3" t="s">
-        <v>1400</v>
+        <v>1406</v>
       </c>
       <c r="D276" s="3" t="s">
         <v>1401</v>
       </c>
       <c r="E276" s="3" t="s">
-        <v>1402</v>
+        <v>1407</v>
       </c>
       <c r="F276" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G276" s="3" t="s">
-        <v>1398</v>
+        <v>1403</v>
       </c>
       <c r="H276" s="3" t="s">
         <v>15</v>
@@ -13924,25 +13975,25 @@
     </row>
     <row r="277" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A277" s="3" t="s">
-        <v>1403</v>
+        <v>1408</v>
       </c>
       <c r="B277" s="3" t="s">
         <v>198</v>
       </c>
       <c r="C277" s="3" t="s">
-        <v>1404</v>
+        <v>1409</v>
       </c>
       <c r="D277" s="3" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="E277" s="3" t="s">
-        <v>1406</v>
+        <v>1410</v>
       </c>
       <c r="F277" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G277" s="3" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="H277" s="3" t="s">
         <v>15</v>
@@ -13950,51 +14001,51 @@
     </row>
     <row r="278" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A278" s="3" t="s">
-        <v>1408</v>
+        <v>1411</v>
       </c>
       <c r="B278" s="3" t="s">
         <v>198</v>
       </c>
       <c r="C278" s="3" t="s">
-        <v>1409</v>
+        <v>1412</v>
       </c>
       <c r="D278" s="3" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="E278" s="3" t="s">
-        <v>1411</v>
+        <v>1414</v>
       </c>
       <c r="F278" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G278" s="3" t="s">
-        <v>1412</v>
+        <v>1415</v>
       </c>
       <c r="H278" s="3" t="s">
-        <v>1413</v>
+        <v>15</v>
       </c>
     </row>
     <row r="279" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A279" s="3" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
       <c r="B279" s="3" t="s">
         <v>198</v>
       </c>
       <c r="C279" s="3" t="s">
-        <v>1415</v>
+        <v>1417</v>
       </c>
       <c r="D279" s="3" t="s">
-        <v>1416</v>
+        <v>1418</v>
       </c>
       <c r="E279" s="3" t="s">
-        <v>1417</v>
+        <v>1419</v>
       </c>
       <c r="F279" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G279" s="3" t="s">
-        <v>1412</v>
+        <v>1415</v>
       </c>
       <c r="H279" s="3" t="s">
         <v>15</v>
@@ -14002,129 +14053,129 @@
     </row>
     <row r="280" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A280" s="3" t="s">
-        <v>1418</v>
+        <v>1420</v>
       </c>
       <c r="B280" s="3" t="s">
         <v>198</v>
       </c>
       <c r="C280" s="3" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="D280" s="3" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
       <c r="E280" s="3" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="F280" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G280" s="3" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="H280" s="3" t="s">
-        <v>1423</v>
+        <v>15</v>
       </c>
     </row>
     <row r="281" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A281" s="3" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="B281" s="3" t="s">
         <v>198</v>
       </c>
       <c r="C281" s="3" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="D281" s="3" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="E281" s="3" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="F281" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G281" s="3" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="H281" s="3" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="282" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A282" s="3" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="B282" s="3" t="s">
         <v>198</v>
       </c>
       <c r="C282" s="3" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="D282" s="3" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="E282" s="3" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="F282" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G282" s="3" t="s">
-        <v>1434</v>
+        <v>1429</v>
       </c>
       <c r="H282" s="3" t="s">
-        <v>1435</v>
+        <v>15</v>
       </c>
     </row>
     <row r="283" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A283" s="3" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="B283" s="3" t="s">
         <v>198</v>
       </c>
       <c r="C283" s="3" t="s">
+        <v>1436</v>
+      </c>
+      <c r="D283" s="3" t="s">
         <v>1437</v>
       </c>
-      <c r="D283" s="3" t="s">
+      <c r="E283" s="3" t="s">
         <v>1438</v>
       </c>
-      <c r="E283" s="3" t="s">
+      <c r="F283" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G283" s="3" t="s">
         <v>1439</v>
       </c>
-      <c r="F283" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G283" s="3" t="s">
+      <c r="H283" s="3" t="s">
         <v>1440</v>
-      </c>
-      <c r="H283" s="3" t="s">
-        <v>1441</v>
       </c>
     </row>
     <row r="284" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A284" s="3" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="B284" s="3" t="s">
         <v>198</v>
       </c>
       <c r="C284" s="3" t="s">
+        <v>1442</v>
+      </c>
+      <c r="D284" s="3" t="s">
         <v>1443</v>
       </c>
-      <c r="D284" s="3" t="s">
+      <c r="E284" s="3" t="s">
         <v>1444</v>
       </c>
-      <c r="E284" s="3" t="s">
+      <c r="F284" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G284" s="3" t="s">
         <v>1445</v>
-      </c>
-      <c r="F284" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G284" s="3" t="s">
-        <v>1440</v>
       </c>
       <c r="H284" s="3" t="s">
         <v>1446</v>
@@ -14153,1434 +14204,1434 @@
         <v>1451</v>
       </c>
       <c r="H285" s="3" t="s">
-        <v>412</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="286" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A286" s="3" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="B286" s="3" t="s">
         <v>198</v>
       </c>
       <c r="C286" s="3" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="D286" s="3" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="E286" s="3" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="F286" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G286" s="3" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="H286" s="3" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="287" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A287" s="3" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="B287" s="3" t="s">
         <v>198</v>
       </c>
       <c r="C287" s="3" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="D287" s="3" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="E287" s="3" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="F287" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G287" s="3" t="s">
-        <v>1451</v>
+        <v>1457</v>
       </c>
       <c r="H287" s="3" t="s">
-        <v>15</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="288" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A288" s="3" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="B288" s="3" t="s">
         <v>198</v>
       </c>
       <c r="C288" s="3" t="s">
-        <v>1463</v>
+        <v>1465</v>
       </c>
       <c r="D288" s="3" t="s">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="E288" s="3" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="F288" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G288" s="3" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="H288" s="3" t="s">
-        <v>1467</v>
+        <v>412</v>
       </c>
     </row>
     <row r="289" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A289" s="3" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="B289" s="3" t="s">
         <v>198</v>
       </c>
       <c r="C289" s="3" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="D289" s="3" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="E289" s="3" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="F289" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G289" s="3" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="H289" s="3" t="s">
-        <v>1467</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="290" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A290" s="3" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="B290" s="3" t="s">
         <v>198</v>
       </c>
       <c r="C290" s="3" t="s">
-        <v>1469</v>
+        <v>1476</v>
       </c>
       <c r="D290" s="3" t="s">
-        <v>1474</v>
+        <v>1477</v>
       </c>
       <c r="E290" s="3" t="s">
-        <v>1475</v>
+        <v>1478</v>
       </c>
       <c r="F290" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G290" s="3" t="s">
-        <v>1472</v>
+        <v>1468</v>
       </c>
       <c r="H290" s="3" t="s">
-        <v>1467</v>
+        <v>15</v>
       </c>
     </row>
     <row r="291" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A291" s="3" t="s">
-        <v>1476</v>
+        <v>1479</v>
       </c>
       <c r="B291" s="3" t="s">
         <v>198</v>
       </c>
       <c r="C291" s="3" t="s">
-        <v>1477</v>
+        <v>1480</v>
       </c>
       <c r="D291" s="3" t="s">
-        <v>1478</v>
+        <v>1481</v>
       </c>
       <c r="E291" s="3" t="s">
-        <v>1479</v>
+        <v>1482</v>
       </c>
       <c r="F291" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G291" s="3" t="s">
-        <v>1451</v>
+        <v>1483</v>
       </c>
       <c r="H291" s="3" t="s">
-        <v>15</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="292" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A292" s="3" t="s">
-        <v>1480</v>
+        <v>1485</v>
       </c>
       <c r="B292" s="3" t="s">
         <v>198</v>
       </c>
       <c r="C292" s="3" t="s">
-        <v>1481</v>
+        <v>1486</v>
       </c>
       <c r="D292" s="3" t="s">
-        <v>1482</v>
+        <v>1487</v>
       </c>
       <c r="E292" s="3" t="s">
-        <v>1483</v>
+        <v>1488</v>
       </c>
       <c r="F292" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G292" s="3" t="s">
-        <v>1451</v>
+        <v>1489</v>
       </c>
       <c r="H292" s="3" t="s">
-        <v>15</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="293" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A293" s="3" t="s">
-        <v>1484</v>
+        <v>1490</v>
       </c>
       <c r="B293" s="3" t="s">
         <v>198</v>
       </c>
       <c r="C293" s="3" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="D293" s="3" t="s">
-        <v>1486</v>
+        <v>1491</v>
       </c>
       <c r="E293" s="3" t="s">
-        <v>1487</v>
+        <v>1492</v>
       </c>
       <c r="F293" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G293" s="3" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="H293" s="3" t="s">
-        <v>1489</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="294" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A294" s="3" t="s">
-        <v>1490</v>
+        <v>1493</v>
       </c>
       <c r="B294" s="3" t="s">
         <v>198</v>
       </c>
       <c r="C294" s="3" t="s">
-        <v>1491</v>
+        <v>1494</v>
       </c>
       <c r="D294" s="3" t="s">
-        <v>1492</v>
+        <v>1495</v>
       </c>
       <c r="E294" s="3" t="s">
-        <v>1493</v>
+        <v>1496</v>
       </c>
       <c r="F294" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G294" s="3" t="s">
-        <v>1494</v>
+        <v>1468</v>
       </c>
       <c r="H294" s="3" t="s">
-        <v>1489</v>
+        <v>15</v>
       </c>
     </row>
     <row r="295" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A295" s="3" t="s">
-        <v>1495</v>
+        <v>1497</v>
       </c>
       <c r="B295" s="3" t="s">
         <v>198</v>
       </c>
       <c r="C295" s="3" t="s">
-        <v>1496</v>
+        <v>1498</v>
       </c>
       <c r="D295" s="3" t="s">
-        <v>1497</v>
+        <v>1499</v>
       </c>
       <c r="E295" s="3" t="s">
-        <v>1498</v>
+        <v>1500</v>
       </c>
       <c r="F295" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G295" s="3" t="s">
-        <v>1499</v>
+        <v>1468</v>
       </c>
       <c r="H295" s="3" t="s">
-        <v>1489</v>
+        <v>15</v>
       </c>
     </row>
     <row r="296" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A296" s="3" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="B296" s="3" t="s">
-        <v>48</v>
+        <v>198</v>
       </c>
       <c r="C296" s="3" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="D296" s="3" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="E296" s="3" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="F296" s="3" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="G296" s="3" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="H296" s="3" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="297" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A297" s="3" t="s">
+        <v>1507</v>
+      </c>
+      <c r="B297" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C297" s="3" t="s">
+        <v>1508</v>
+      </c>
+      <c r="D297" s="3" t="s">
+        <v>1509</v>
+      </c>
+      <c r="E297" s="3" t="s">
+        <v>1510</v>
+      </c>
+      <c r="F297" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G297" s="3" t="s">
+        <v>1511</v>
+      </c>
+      <c r="H297" s="3" t="s">
         <v>1506</v>
-      </c>
-      <c r="B297" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C297" s="3" t="s">
-        <v>1507</v>
-      </c>
-      <c r="D297" s="3" t="s">
-        <v>1508</v>
-      </c>
-      <c r="E297" s="3" t="s">
-        <v>1509</v>
-      </c>
-      <c r="F297" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G297" s="3" t="s">
-        <v>1504</v>
-      </c>
-      <c r="H297" s="3" t="s">
-        <v>1510</v>
       </c>
     </row>
     <row r="298" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A298" s="3" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="B298" s="3" t="s">
-        <v>48</v>
+        <v>198</v>
       </c>
       <c r="C298" s="3" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="D298" s="3" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="E298" s="3" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="F298" s="3" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="G298" s="3" t="s">
-        <v>1504</v>
+        <v>1516</v>
       </c>
       <c r="H298" s="3" t="s">
-        <v>1515</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="299" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A299" s="3" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="B299" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C299" s="3" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="D299" s="3" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="E299" s="3" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="F299" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G299" s="3" t="s">
-        <v>1504</v>
+        <v>1521</v>
       </c>
       <c r="H299" s="3" t="s">
-        <v>1520</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="300" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A300" s="3" t="s">
-        <v>1521</v>
+        <v>1523</v>
       </c>
       <c r="B300" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C300" s="3" t="s">
-        <v>1522</v>
+        <v>1524</v>
       </c>
       <c r="D300" s="3" t="s">
-        <v>1513</v>
+        <v>1525</v>
       </c>
       <c r="E300" s="3" t="s">
-        <v>1514</v>
+        <v>1526</v>
       </c>
       <c r="F300" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G300" s="3" t="s">
-        <v>1504</v>
+        <v>1521</v>
       </c>
       <c r="H300" s="3" t="s">
-        <v>1523</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="301" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A301" s="3" t="s">
-        <v>1524</v>
+        <v>1528</v>
       </c>
       <c r="B301" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C301" s="3" t="s">
-        <v>1525</v>
+        <v>1529</v>
       </c>
       <c r="D301" s="3" t="s">
-        <v>1526</v>
+        <v>1530</v>
       </c>
       <c r="E301" s="3" t="s">
-        <v>1527</v>
+        <v>1531</v>
       </c>
       <c r="F301" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G301" s="3" t="s">
-        <v>1504</v>
+        <v>1521</v>
       </c>
       <c r="H301" s="3" t="s">
-        <v>1528</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="302" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A302" s="3" t="s">
-        <v>1529</v>
+        <v>1533</v>
       </c>
       <c r="B302" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C302" s="3" t="s">
-        <v>1530</v>
+        <v>1534</v>
       </c>
       <c r="D302" s="3" t="s">
-        <v>1513</v>
+        <v>1535</v>
       </c>
       <c r="E302" s="3" t="s">
-        <v>1514</v>
+        <v>1536</v>
       </c>
       <c r="F302" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G302" s="3" t="s">
-        <v>1504</v>
+        <v>1521</v>
       </c>
       <c r="H302" s="3" t="s">
-        <v>1531</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="303" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A303" s="3" t="s">
-        <v>1532</v>
+        <v>1538</v>
       </c>
       <c r="B303" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C303" s="3" t="s">
-        <v>1533</v>
+        <v>1539</v>
       </c>
       <c r="D303" s="3" t="s">
-        <v>1534</v>
+        <v>1530</v>
       </c>
       <c r="E303" s="3" t="s">
-        <v>1535</v>
+        <v>1531</v>
       </c>
       <c r="F303" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G303" s="3" t="s">
-        <v>1504</v>
+        <v>1521</v>
       </c>
       <c r="H303" s="3" t="s">
-        <v>1536</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="304" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A304" s="3" t="s">
-        <v>1537</v>
+        <v>1541</v>
       </c>
       <c r="B304" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C304" s="3" t="s">
-        <v>1538</v>
+        <v>1542</v>
       </c>
       <c r="D304" s="3" t="s">
-        <v>1513</v>
+        <v>1543</v>
       </c>
       <c r="E304" s="3" t="s">
-        <v>1514</v>
+        <v>1544</v>
       </c>
       <c r="F304" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G304" s="3" t="s">
-        <v>1504</v>
+        <v>1521</v>
       </c>
       <c r="H304" s="3" t="s">
-        <v>1539</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="305" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A305" s="3" t="s">
-        <v>1540</v>
+        <v>1546</v>
       </c>
       <c r="B305" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C305" s="3" t="s">
-        <v>1541</v>
+        <v>1547</v>
       </c>
       <c r="D305" s="3" t="s">
-        <v>1542</v>
+        <v>1530</v>
       </c>
       <c r="E305" s="3" t="s">
-        <v>1543</v>
+        <v>1531</v>
       </c>
       <c r="F305" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G305" s="3" t="s">
-        <v>1504</v>
+        <v>1521</v>
       </c>
       <c r="H305" s="3" t="s">
-        <v>1544</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="306" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A306" s="3" t="s">
-        <v>1545</v>
+        <v>1549</v>
       </c>
       <c r="B306" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C306" s="3" t="s">
-        <v>1546</v>
+        <v>1550</v>
       </c>
       <c r="D306" s="3" t="s">
-        <v>1513</v>
+        <v>1551</v>
       </c>
       <c r="E306" s="3" t="s">
-        <v>1514</v>
+        <v>1552</v>
       </c>
       <c r="F306" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G306" s="3" t="s">
-        <v>1504</v>
+        <v>1521</v>
       </c>
       <c r="H306" s="3" t="s">
-        <v>1547</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="307" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A307" s="3" t="s">
-        <v>1548</v>
+        <v>1554</v>
       </c>
       <c r="B307" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C307" s="3" t="s">
-        <v>1549</v>
+        <v>1555</v>
       </c>
       <c r="D307" s="3" t="s">
-        <v>1550</v>
+        <v>1530</v>
       </c>
       <c r="E307" s="3" t="s">
-        <v>1551</v>
+        <v>1531</v>
       </c>
       <c r="F307" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G307" s="3" t="s">
-        <v>1504</v>
+        <v>1521</v>
       </c>
       <c r="H307" s="3" t="s">
-        <v>1552</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="308" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A308" s="3" t="s">
-        <v>1553</v>
+        <v>1557</v>
       </c>
       <c r="B308" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C308" s="3" t="s">
-        <v>1554</v>
+        <v>1558</v>
       </c>
       <c r="D308" s="3" t="s">
-        <v>1513</v>
+        <v>1559</v>
       </c>
       <c r="E308" s="3" t="s">
-        <v>1514</v>
+        <v>1560</v>
       </c>
       <c r="F308" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G308" s="3" t="s">
-        <v>1504</v>
+        <v>1521</v>
       </c>
       <c r="H308" s="3" t="s">
-        <v>1555</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="309" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A309" s="3" t="s">
-        <v>1556</v>
+        <v>1562</v>
       </c>
       <c r="B309" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C309" s="3" t="s">
-        <v>1557</v>
+        <v>1563</v>
       </c>
       <c r="D309" s="3" t="s">
-        <v>1558</v>
+        <v>1530</v>
       </c>
       <c r="E309" s="3" t="s">
-        <v>1559</v>
+        <v>1531</v>
       </c>
       <c r="F309" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G309" s="3" t="s">
-        <v>1504</v>
+        <v>1521</v>
       </c>
       <c r="H309" s="3" t="s">
-        <v>1560</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="310" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A310" s="3" t="s">
-        <v>1561</v>
+        <v>1565</v>
       </c>
       <c r="B310" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C310" s="3" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="D310" s="3" t="s">
-        <v>1513</v>
+        <v>1567</v>
       </c>
       <c r="E310" s="3" t="s">
-        <v>1514</v>
+        <v>1568</v>
       </c>
       <c r="F310" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G310" s="3" t="s">
-        <v>1504</v>
+        <v>1521</v>
       </c>
       <c r="H310" s="3" t="s">
-        <v>1563</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="311" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A311" s="3" t="s">
-        <v>1564</v>
+        <v>1570</v>
       </c>
       <c r="B311" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C311" s="3" t="s">
-        <v>1565</v>
+        <v>1571</v>
       </c>
       <c r="D311" s="3" t="s">
-        <v>1566</v>
+        <v>1530</v>
       </c>
       <c r="E311" s="3" t="s">
-        <v>1567</v>
+        <v>1531</v>
       </c>
       <c r="F311" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G311" s="3" t="s">
-        <v>1504</v>
+        <v>1521</v>
       </c>
       <c r="H311" s="3" t="s">
-        <v>1568</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="312" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A312" s="3" t="s">
-        <v>1569</v>
+        <v>1573</v>
       </c>
       <c r="B312" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C312" s="3" t="s">
-        <v>1570</v>
+        <v>1574</v>
       </c>
       <c r="D312" s="3" t="s">
-        <v>1513</v>
+        <v>1575</v>
       </c>
       <c r="E312" s="3" t="s">
-        <v>1514</v>
+        <v>1576</v>
       </c>
       <c r="F312" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G312" s="3" t="s">
-        <v>1504</v>
+        <v>1521</v>
       </c>
       <c r="H312" s="3" t="s">
-        <v>1571</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="313" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A313" s="3" t="s">
-        <v>1572</v>
+        <v>1578</v>
       </c>
       <c r="B313" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C313" s="3" t="s">
-        <v>1573</v>
+        <v>1579</v>
       </c>
       <c r="D313" s="3" t="s">
-        <v>1574</v>
+        <v>1530</v>
       </c>
       <c r="E313" s="3" t="s">
-        <v>1575</v>
+        <v>1531</v>
       </c>
       <c r="F313" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G313" s="3" t="s">
-        <v>1504</v>
+        <v>1521</v>
       </c>
       <c r="H313" s="3" t="s">
-        <v>1576</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="314" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A314" s="3" t="s">
-        <v>1577</v>
+        <v>1581</v>
       </c>
       <c r="B314" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C314" s="3" t="s">
-        <v>1578</v>
+        <v>1582</v>
       </c>
       <c r="D314" s="3" t="s">
-        <v>1513</v>
+        <v>1583</v>
       </c>
       <c r="E314" s="3" t="s">
-        <v>1514</v>
+        <v>1584</v>
       </c>
       <c r="F314" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G314" s="3" t="s">
-        <v>1504</v>
+        <v>1521</v>
       </c>
       <c r="H314" s="3" t="s">
-        <v>1579</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="315" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A315" s="3" t="s">
-        <v>1580</v>
+        <v>1586</v>
       </c>
       <c r="B315" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C315" s="3" t="s">
-        <v>1581</v>
+        <v>1587</v>
       </c>
       <c r="D315" s="3" t="s">
-        <v>1582</v>
+        <v>1530</v>
       </c>
       <c r="E315" s="3" t="s">
-        <v>1583</v>
+        <v>1531</v>
       </c>
       <c r="F315" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G315" s="3" t="s">
-        <v>1504</v>
+        <v>1521</v>
       </c>
       <c r="H315" s="3" t="s">
-        <v>1584</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="316" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A316" s="3" t="s">
-        <v>1585</v>
+        <v>1589</v>
       </c>
       <c r="B316" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C316" s="3" t="s">
-        <v>1586</v>
+        <v>1590</v>
       </c>
       <c r="D316" s="3" t="s">
-        <v>1513</v>
+        <v>1591</v>
       </c>
       <c r="E316" s="3" t="s">
-        <v>1514</v>
+        <v>1592</v>
       </c>
       <c r="F316" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G316" s="3" t="s">
-        <v>1504</v>
+        <v>1521</v>
       </c>
       <c r="H316" s="3" t="s">
-        <v>1587</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="317" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A317" s="3" t="s">
-        <v>1588</v>
+        <v>1594</v>
       </c>
       <c r="B317" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C317" s="3" t="s">
-        <v>1589</v>
+        <v>1595</v>
       </c>
       <c r="D317" s="3" t="s">
-        <v>1590</v>
+        <v>1530</v>
       </c>
       <c r="E317" s="3" t="s">
-        <v>1591</v>
+        <v>1531</v>
       </c>
       <c r="F317" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G317" s="3" t="s">
-        <v>1504</v>
+        <v>1521</v>
       </c>
       <c r="H317" s="3" t="s">
-        <v>1592</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="318" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A318" s="3" t="s">
-        <v>1593</v>
+        <v>1597</v>
       </c>
       <c r="B318" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C318" s="3" t="s">
-        <v>1594</v>
+        <v>1598</v>
       </c>
       <c r="D318" s="3" t="s">
-        <v>1513</v>
+        <v>1599</v>
       </c>
       <c r="E318" s="3" t="s">
-        <v>1514</v>
+        <v>1600</v>
       </c>
       <c r="F318" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G318" s="3" t="s">
-        <v>1504</v>
+        <v>1521</v>
       </c>
       <c r="H318" s="3" t="s">
-        <v>1595</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="319" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A319" s="3" t="s">
-        <v>1596</v>
+        <v>1602</v>
       </c>
       <c r="B319" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C319" s="3" t="s">
-        <v>1597</v>
+        <v>1603</v>
       </c>
       <c r="D319" s="3" t="s">
-        <v>1598</v>
+        <v>1530</v>
       </c>
       <c r="E319" s="3" t="s">
-        <v>1599</v>
+        <v>1531</v>
       </c>
       <c r="F319" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G319" s="3" t="s">
-        <v>1504</v>
+        <v>1521</v>
       </c>
       <c r="H319" s="3" t="s">
-        <v>1600</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="320" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A320" s="3" t="s">
-        <v>1601</v>
+        <v>1605</v>
       </c>
       <c r="B320" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C320" s="3" t="s">
-        <v>1602</v>
+        <v>1606</v>
       </c>
       <c r="D320" s="3" t="s">
-        <v>1513</v>
+        <v>1607</v>
       </c>
       <c r="E320" s="3" t="s">
-        <v>1514</v>
+        <v>1608</v>
       </c>
       <c r="F320" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G320" s="3" t="s">
-        <v>1504</v>
+        <v>1521</v>
       </c>
       <c r="H320" s="3" t="s">
-        <v>1603</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="321" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A321" s="3" t="s">
-        <v>1604</v>
+        <v>1610</v>
       </c>
       <c r="B321" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C321" s="3" t="s">
-        <v>1605</v>
+        <v>1611</v>
       </c>
       <c r="D321" s="3" t="s">
-        <v>1606</v>
+        <v>1530</v>
       </c>
       <c r="E321" s="3" t="s">
-        <v>1607</v>
+        <v>1531</v>
       </c>
       <c r="F321" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G321" s="3" t="s">
-        <v>1504</v>
+        <v>1521</v>
       </c>
       <c r="H321" s="3" t="s">
-        <v>1608</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="322" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A322" s="3" t="s">
-        <v>1609</v>
+        <v>1613</v>
       </c>
       <c r="B322" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C322" s="3" t="s">
-        <v>1610</v>
+        <v>1614</v>
       </c>
       <c r="D322" s="3" t="s">
-        <v>1513</v>
+        <v>1615</v>
       </c>
       <c r="E322" s="3" t="s">
-        <v>1514</v>
+        <v>1616</v>
       </c>
       <c r="F322" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G322" s="3" t="s">
-        <v>1504</v>
+        <v>1521</v>
       </c>
       <c r="H322" s="3" t="s">
-        <v>1611</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="323" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A323" s="3" t="s">
-        <v>1612</v>
+        <v>1618</v>
       </c>
       <c r="B323" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C323" s="3" t="s">
-        <v>1613</v>
+        <v>1619</v>
       </c>
       <c r="D323" s="3" t="s">
-        <v>1614</v>
+        <v>1530</v>
       </c>
       <c r="E323" s="3" t="s">
-        <v>1615</v>
+        <v>1531</v>
       </c>
       <c r="F323" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G323" s="3" t="s">
-        <v>1504</v>
+        <v>1521</v>
       </c>
       <c r="H323" s="3" t="s">
-        <v>1616</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="324" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A324" s="3" t="s">
-        <v>1617</v>
+        <v>1621</v>
       </c>
       <c r="B324" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C324" s="3" t="s">
-        <v>1618</v>
+        <v>1622</v>
       </c>
       <c r="D324" s="3" t="s">
-        <v>1513</v>
+        <v>1623</v>
       </c>
       <c r="E324" s="3" t="s">
-        <v>1514</v>
+        <v>1624</v>
       </c>
       <c r="F324" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G324" s="3" t="s">
-        <v>1504</v>
+        <v>1521</v>
       </c>
       <c r="H324" s="3" t="s">
-        <v>1619</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="325" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A325" s="3" t="s">
-        <v>1620</v>
+        <v>1626</v>
       </c>
       <c r="B325" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C325" s="3" t="s">
-        <v>1621</v>
+        <v>1627</v>
       </c>
       <c r="D325" s="3" t="s">
-        <v>1622</v>
+        <v>1530</v>
       </c>
       <c r="E325" s="3" t="s">
-        <v>1623</v>
+        <v>1531</v>
       </c>
       <c r="F325" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G325" s="3" t="s">
-        <v>1504</v>
+        <v>1521</v>
       </c>
       <c r="H325" s="3" t="s">
-        <v>1624</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="326" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A326" s="3" t="s">
-        <v>1625</v>
+        <v>1629</v>
       </c>
       <c r="B326" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C326" s="3" t="s">
-        <v>1626</v>
+        <v>1630</v>
       </c>
       <c r="D326" s="3" t="s">
-        <v>1513</v>
+        <v>1631</v>
       </c>
       <c r="E326" s="3" t="s">
-        <v>1514</v>
+        <v>1632</v>
       </c>
       <c r="F326" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G326" s="3" t="s">
-        <v>1504</v>
+        <v>1521</v>
       </c>
       <c r="H326" s="3" t="s">
-        <v>1627</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="327" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A327" s="3" t="s">
-        <v>1628</v>
+        <v>1634</v>
       </c>
       <c r="B327" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C327" s="3" t="s">
-        <v>1629</v>
+        <v>1635</v>
       </c>
       <c r="D327" s="3" t="s">
-        <v>1630</v>
+        <v>1530</v>
       </c>
       <c r="E327" s="3" t="s">
-        <v>1631</v>
+        <v>1531</v>
       </c>
       <c r="F327" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G327" s="3" t="s">
-        <v>1504</v>
+        <v>1521</v>
       </c>
       <c r="H327" s="3" t="s">
-        <v>1632</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="328" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A328" s="3" t="s">
-        <v>1633</v>
+        <v>1637</v>
       </c>
       <c r="B328" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C328" s="3" t="s">
-        <v>1634</v>
+        <v>1638</v>
       </c>
       <c r="D328" s="3" t="s">
-        <v>1513</v>
+        <v>1639</v>
       </c>
       <c r="E328" s="3" t="s">
-        <v>1514</v>
+        <v>1640</v>
       </c>
       <c r="F328" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G328" s="3" t="s">
-        <v>1504</v>
+        <v>1521</v>
       </c>
       <c r="H328" s="3" t="s">
-        <v>1635</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="329" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A329" s="3" t="s">
-        <v>1636</v>
+        <v>1642</v>
       </c>
       <c r="B329" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C329" s="3" t="s">
-        <v>1637</v>
+        <v>1643</v>
       </c>
       <c r="D329" s="3" t="s">
-        <v>1638</v>
+        <v>1530</v>
       </c>
       <c r="E329" s="3" t="s">
-        <v>1639</v>
+        <v>1531</v>
       </c>
       <c r="F329" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G329" s="3" t="s">
-        <v>1504</v>
+        <v>1521</v>
       </c>
       <c r="H329" s="3" t="s">
-        <v>1640</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="330" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A330" s="3" t="s">
-        <v>1641</v>
+        <v>1645</v>
       </c>
       <c r="B330" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C330" s="3" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="D330" s="3" t="s">
-        <v>1513</v>
+        <v>1647</v>
       </c>
       <c r="E330" s="3" t="s">
-        <v>1514</v>
+        <v>1648</v>
       </c>
       <c r="F330" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G330" s="3" t="s">
-        <v>1504</v>
+        <v>1521</v>
       </c>
       <c r="H330" s="3" t="s">
-        <v>1643</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="331" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A331" s="3" t="s">
-        <v>1644</v>
+        <v>1650</v>
       </c>
       <c r="B331" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C331" s="3" t="s">
-        <v>1645</v>
+        <v>1651</v>
       </c>
       <c r="D331" s="3" t="s">
-        <v>1646</v>
+        <v>1530</v>
       </c>
       <c r="E331" s="3" t="s">
-        <v>1647</v>
+        <v>1531</v>
       </c>
       <c r="F331" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G331" s="3" t="s">
-        <v>1504</v>
+        <v>1521</v>
       </c>
       <c r="H331" s="3" t="s">
-        <v>1648</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="332" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A332" s="3" t="s">
-        <v>1649</v>
+        <v>1653</v>
       </c>
       <c r="B332" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C332" s="3" t="s">
-        <v>1650</v>
+        <v>1654</v>
       </c>
       <c r="D332" s="3" t="s">
-        <v>1513</v>
+        <v>1655</v>
       </c>
       <c r="E332" s="3" t="s">
-        <v>1514</v>
+        <v>1656</v>
       </c>
       <c r="F332" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G332" s="3" t="s">
-        <v>1504</v>
+        <v>1521</v>
       </c>
       <c r="H332" s="3" t="s">
-        <v>1651</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="333" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A333" s="3" t="s">
-        <v>1652</v>
+        <v>1658</v>
       </c>
       <c r="B333" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C333" s="3" t="s">
-        <v>1653</v>
+        <v>1659</v>
       </c>
       <c r="D333" s="3" t="s">
-        <v>1654</v>
+        <v>1530</v>
       </c>
       <c r="E333" s="3" t="s">
-        <v>1655</v>
+        <v>1531</v>
       </c>
       <c r="F333" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G333" s="3" t="s">
-        <v>1504</v>
+        <v>1521</v>
       </c>
       <c r="H333" s="3" t="s">
-        <v>1656</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="334" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A334" s="3" t="s">
-        <v>1657</v>
+        <v>1661</v>
       </c>
       <c r="B334" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C334" s="3" t="s">
-        <v>1658</v>
+        <v>1662</v>
       </c>
       <c r="D334" s="3" t="s">
-        <v>1513</v>
+        <v>1663</v>
       </c>
       <c r="E334" s="3" t="s">
-        <v>1514</v>
+        <v>1664</v>
       </c>
       <c r="F334" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G334" s="3" t="s">
-        <v>1504</v>
+        <v>1521</v>
       </c>
       <c r="H334" s="3" t="s">
-        <v>1659</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="335" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A335" s="3" t="s">
-        <v>1660</v>
+        <v>1666</v>
       </c>
       <c r="B335" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C335" s="3" t="s">
-        <v>1661</v>
+        <v>1667</v>
       </c>
       <c r="D335" s="3" t="s">
-        <v>1662</v>
+        <v>1530</v>
       </c>
       <c r="E335" s="3" t="s">
-        <v>1663</v>
+        <v>1531</v>
       </c>
       <c r="F335" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G335" s="3" t="s">
-        <v>1504</v>
+        <v>1521</v>
       </c>
       <c r="H335" s="3" t="s">
-        <v>1664</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="336" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A336" s="3" t="s">
-        <v>1665</v>
+        <v>1669</v>
       </c>
       <c r="B336" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C336" s="3" t="s">
-        <v>1666</v>
+        <v>1670</v>
       </c>
       <c r="D336" s="3" t="s">
-        <v>1513</v>
+        <v>1671</v>
       </c>
       <c r="E336" s="3" t="s">
-        <v>1514</v>
+        <v>1672</v>
       </c>
       <c r="F336" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G336" s="3" t="s">
-        <v>1504</v>
+        <v>1521</v>
       </c>
       <c r="H336" s="3" t="s">
-        <v>1667</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="337" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A337" s="3" t="s">
-        <v>1668</v>
+        <v>1674</v>
       </c>
       <c r="B337" s="3" t="s">
-        <v>1669</v>
+        <v>48</v>
       </c>
       <c r="C337" s="3" t="s">
-        <v>1670</v>
+        <v>1675</v>
       </c>
       <c r="D337" s="3" t="s">
-        <v>1671</v>
+        <v>1530</v>
       </c>
       <c r="E337" s="3" t="s">
-        <v>1672</v>
+        <v>1531</v>
       </c>
       <c r="F337" s="3" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G337" s="3" t="s">
-        <v>1673</v>
+        <v>1521</v>
       </c>
       <c r="H337" s="3" t="s">
-        <v>15</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="338" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A338" s="3" t="s">
-        <v>1674</v>
+        <v>1677</v>
       </c>
       <c r="B338" s="3" t="s">
-        <v>1669</v>
+        <v>48</v>
       </c>
       <c r="C338" s="3" t="s">
-        <v>1675</v>
+        <v>1678</v>
       </c>
       <c r="D338" s="3" t="s">
-        <v>1671</v>
+        <v>1679</v>
       </c>
       <c r="E338" s="3" t="s">
-        <v>1672</v>
+        <v>1680</v>
       </c>
       <c r="F338" s="3" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G338" s="3" t="s">
-        <v>1673</v>
+        <v>1521</v>
       </c>
       <c r="H338" s="3" t="s">
-        <v>15</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="339" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A339" s="3" t="s">
-        <v>1676</v>
+        <v>1682</v>
       </c>
       <c r="B339" s="3" t="s">
-        <v>1669</v>
+        <v>48</v>
       </c>
       <c r="C339" s="3" t="s">
-        <v>1677</v>
+        <v>1683</v>
       </c>
       <c r="D339" s="3" t="s">
-        <v>1671</v>
+        <v>1530</v>
       </c>
       <c r="E339" s="3" t="s">
-        <v>1672</v>
+        <v>1531</v>
       </c>
       <c r="F339" s="3" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G339" s="3" t="s">
-        <v>1673</v>
+        <v>1521</v>
       </c>
       <c r="H339" s="3" t="s">
-        <v>1678</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="340" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A340" s="3" t="s">
-        <v>1679</v>
+        <v>1685</v>
       </c>
       <c r="B340" s="3" t="s">
-        <v>1669</v>
+        <v>1686</v>
       </c>
       <c r="C340" s="3" t="s">
-        <v>458</v>
+        <v>1687</v>
       </c>
       <c r="D340" s="3" t="s">
-        <v>1680</v>
+        <v>1688</v>
       </c>
       <c r="E340" s="3" t="s">
-        <v>1681</v>
+        <v>1689</v>
       </c>
       <c r="F340" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G340" s="3" t="s">
-        <v>1682</v>
+        <v>1690</v>
       </c>
       <c r="H340" s="3" t="s">
         <v>15</v>
@@ -15588,25 +15639,25 @@
     </row>
     <row r="341" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A341" s="3" t="s">
-        <v>1683</v>
+        <v>1691</v>
       </c>
       <c r="B341" s="3" t="s">
-        <v>1669</v>
+        <v>1686</v>
       </c>
       <c r="C341" s="3" t="s">
-        <v>458</v>
+        <v>1692</v>
       </c>
       <c r="D341" s="3" t="s">
-        <v>1684</v>
+        <v>1688</v>
       </c>
       <c r="E341" s="3" t="s">
-        <v>1685</v>
+        <v>1689</v>
       </c>
       <c r="F341" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G341" s="3" t="s">
-        <v>1682</v>
+        <v>1690</v>
       </c>
       <c r="H341" s="3" t="s">
         <v>15</v>
@@ -15614,51 +15665,51 @@
     </row>
     <row r="342" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A342" s="3" t="s">
+        <v>1693</v>
+      </c>
+      <c r="B342" s="3" t="s">
         <v>1686</v>
       </c>
-      <c r="B342" s="3" t="s">
-        <v>1669</v>
-      </c>
       <c r="C342" s="3" t="s">
-        <v>458</v>
+        <v>1694</v>
       </c>
       <c r="D342" s="3" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="E342" s="3" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="F342" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G342" s="3" t="s">
-        <v>1682</v>
+        <v>1690</v>
       </c>
       <c r="H342" s="3" t="s">
-        <v>15</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="343" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A343" s="3" t="s">
-        <v>1689</v>
+        <v>1696</v>
       </c>
       <c r="B343" s="3" t="s">
-        <v>1669</v>
+        <v>1686</v>
       </c>
       <c r="C343" s="3" t="s">
         <v>458</v>
       </c>
       <c r="D343" s="3" t="s">
-        <v>1690</v>
+        <v>1697</v>
       </c>
       <c r="E343" s="3" t="s">
-        <v>1691</v>
+        <v>1698</v>
       </c>
       <c r="F343" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G343" s="3" t="s">
-        <v>1682</v>
+        <v>1699</v>
       </c>
       <c r="H343" s="3" t="s">
         <v>15</v>
@@ -15666,25 +15717,25 @@
     </row>
     <row r="344" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A344" s="3" t="s">
-        <v>1692</v>
+        <v>1700</v>
       </c>
       <c r="B344" s="3" t="s">
-        <v>1669</v>
+        <v>1686</v>
       </c>
       <c r="C344" s="3" t="s">
         <v>458</v>
       </c>
       <c r="D344" s="3" t="s">
-        <v>1693</v>
+        <v>1701</v>
       </c>
       <c r="E344" s="3" t="s">
-        <v>1694</v>
+        <v>1702</v>
       </c>
       <c r="F344" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G344" s="3" t="s">
-        <v>1682</v>
+        <v>1699</v>
       </c>
       <c r="H344" s="3" t="s">
         <v>15</v>
@@ -15692,22 +15743,22 @@
     </row>
     <row r="345" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A345" s="3" t="s">
-        <v>1695</v>
+        <v>1703</v>
       </c>
       <c r="B345" s="3" t="s">
-        <v>344</v>
+        <v>1686</v>
       </c>
       <c r="C345" s="3" t="s">
-        <v>1696</v>
+        <v>458</v>
       </c>
       <c r="D345" s="3" t="s">
-        <v>1697</v>
+        <v>1704</v>
       </c>
       <c r="E345" s="3" t="s">
-        <v>1698</v>
+        <v>1705</v>
       </c>
       <c r="F345" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G345" s="3" t="s">
         <v>1699</v>
@@ -15718,51 +15769,51 @@
     </row>
     <row r="346" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A346" s="3" t="s">
-        <v>1700</v>
+        <v>1706</v>
       </c>
       <c r="B346" s="3" t="s">
-        <v>344</v>
+        <v>1686</v>
       </c>
       <c r="C346" s="3" t="s">
-        <v>1701</v>
+        <v>458</v>
       </c>
       <c r="D346" s="3" t="s">
-        <v>1702</v>
+        <v>1707</v>
       </c>
       <c r="E346" s="3" t="s">
-        <v>1703</v>
+        <v>1708</v>
       </c>
       <c r="F346" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G346" s="3" t="s">
-        <v>1704</v>
+        <v>1699</v>
       </c>
       <c r="H346" s="3" t="s">
-        <v>1705</v>
+        <v>15</v>
       </c>
     </row>
     <row r="347" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A347" s="3" t="s">
-        <v>1706</v>
+        <v>1709</v>
       </c>
       <c r="B347" s="3" t="s">
-        <v>344</v>
+        <v>1686</v>
       </c>
       <c r="C347" s="3" t="s">
-        <v>1707</v>
+        <v>458</v>
       </c>
       <c r="D347" s="3" t="s">
-        <v>1702</v>
+        <v>1710</v>
       </c>
       <c r="E347" s="3" t="s">
-        <v>1703</v>
+        <v>1711</v>
       </c>
       <c r="F347" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G347" s="3" t="s">
-        <v>1704</v>
+        <v>1699</v>
       </c>
       <c r="H347" s="3" t="s">
         <v>15</v>
@@ -15770,25 +15821,25 @@
     </row>
     <row r="348" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A348" s="3" t="s">
-        <v>1708</v>
+        <v>1712</v>
       </c>
       <c r="B348" s="3" t="s">
-        <v>73</v>
+        <v>344</v>
       </c>
       <c r="C348" s="3" t="s">
-        <v>1709</v>
+        <v>1713</v>
       </c>
       <c r="D348" s="3" t="s">
-        <v>1710</v>
+        <v>1714</v>
       </c>
       <c r="E348" s="3" t="s">
-        <v>1711</v>
+        <v>1715</v>
       </c>
       <c r="F348" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G348" s="3" t="s">
-        <v>1712</v>
+        <v>1716</v>
       </c>
       <c r="H348" s="3" t="s">
         <v>15</v>
@@ -15796,39 +15847,39 @@
     </row>
     <row r="349" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A349" s="3" t="s">
-        <v>1713</v>
+        <v>1717</v>
       </c>
       <c r="B349" s="3" t="s">
         <v>344</v>
       </c>
       <c r="C349" s="3" t="s">
-        <v>1714</v>
+        <v>1718</v>
       </c>
       <c r="D349" s="3" t="s">
-        <v>1715</v>
+        <v>1719</v>
       </c>
       <c r="E349" s="3" t="s">
-        <v>1716</v>
+        <v>1720</v>
       </c>
       <c r="F349" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G349" s="3" t="s">
-        <v>1712</v>
+        <v>1721</v>
       </c>
       <c r="H349" s="3" t="s">
-        <v>15</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="350" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A350" s="3" t="s">
-        <v>1717</v>
+        <v>1723</v>
       </c>
       <c r="B350" s="3" t="s">
-        <v>253</v>
+        <v>344</v>
       </c>
       <c r="C350" s="3" t="s">
-        <v>1718</v>
+        <v>1724</v>
       </c>
       <c r="D350" s="3" t="s">
         <v>1719</v>
@@ -15837,7 +15888,7 @@
         <v>1720</v>
       </c>
       <c r="F350" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G350" s="3" t="s">
         <v>1721</v>
@@ -15848,25 +15899,25 @@
     </row>
     <row r="351" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A351" s="3" t="s">
-        <v>1722</v>
+        <v>1725</v>
       </c>
       <c r="B351" s="3" t="s">
-        <v>253</v>
+        <v>73</v>
       </c>
       <c r="C351" s="3" t="s">
-        <v>1723</v>
+        <v>1726</v>
       </c>
       <c r="D351" s="3" t="s">
-        <v>1724</v>
+        <v>1727</v>
       </c>
       <c r="E351" s="3" t="s">
-        <v>1725</v>
+        <v>1728</v>
       </c>
       <c r="F351" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G351" s="3" t="s">
-        <v>1721</v>
+        <v>1729</v>
       </c>
       <c r="H351" s="3" t="s">
         <v>15</v>
@@ -15874,25 +15925,25 @@
     </row>
     <row r="352" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A352" s="3" t="s">
-        <v>1726</v>
+        <v>1730</v>
       </c>
       <c r="B352" s="3" t="s">
-        <v>253</v>
+        <v>344</v>
       </c>
       <c r="C352" s="3" t="s">
-        <v>1727</v>
+        <v>1731</v>
       </c>
       <c r="D352" s="3" t="s">
-        <v>1728</v>
+        <v>1732</v>
       </c>
       <c r="E352" s="3" t="s">
+        <v>1733</v>
+      </c>
+      <c r="F352" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G352" s="3" t="s">
         <v>1729</v>
-      </c>
-      <c r="F352" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G352" s="3" t="s">
-        <v>1730</v>
       </c>
       <c r="H352" s="3" t="s">
         <v>15</v>
@@ -15900,77 +15951,77 @@
     </row>
     <row r="353" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A353" s="3" t="s">
-        <v>1731</v>
+        <v>1734</v>
       </c>
       <c r="B353" s="3" t="s">
         <v>253</v>
       </c>
       <c r="C353" s="3" t="s">
-        <v>1732</v>
+        <v>1735</v>
       </c>
       <c r="D353" s="3" t="s">
-        <v>1733</v>
+        <v>1736</v>
       </c>
       <c r="E353" s="3" t="s">
-        <v>1734</v>
+        <v>1737</v>
       </c>
       <c r="F353" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G353" s="3" t="s">
-        <v>1730</v>
+        <v>1738</v>
       </c>
       <c r="H353" s="3" t="s">
-        <v>1735</v>
+        <v>15</v>
       </c>
     </row>
     <row r="354" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A354" s="3" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
       <c r="B354" s="3" t="s">
-        <v>407</v>
+        <v>253</v>
       </c>
       <c r="C354" s="3" t="s">
-        <v>1737</v>
+        <v>1740</v>
       </c>
       <c r="D354" s="3" t="s">
+        <v>1741</v>
+      </c>
+      <c r="E354" s="3" t="s">
+        <v>1742</v>
+      </c>
+      <c r="F354" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G354" s="3" t="s">
         <v>1738</v>
       </c>
-      <c r="E354" s="3" t="s">
-        <v>1739</v>
-      </c>
-      <c r="F354" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G354" s="3" t="s">
-        <v>1740</v>
-      </c>
       <c r="H354" s="3" t="s">
-        <v>1741</v>
+        <v>15</v>
       </c>
     </row>
     <row r="355" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A355" s="3" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="B355" s="3" t="s">
-        <v>407</v>
+        <v>253</v>
       </c>
       <c r="C355" s="3" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="D355" s="3" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="E355" s="3" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="F355" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G355" s="3" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="H355" s="3" t="s">
         <v>15</v>
@@ -15978,184 +16029,184 @@
     </row>
     <row r="356" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A356" s="3" t="s">
+        <v>1748</v>
+      </c>
+      <c r="B356" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C356" s="3" t="s">
+        <v>1749</v>
+      </c>
+      <c r="D356" s="3" t="s">
+        <v>1750</v>
+      </c>
+      <c r="E356" s="3" t="s">
+        <v>1751</v>
+      </c>
+      <c r="F356" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G356" s="3" t="s">
         <v>1747</v>
       </c>
-      <c r="B356" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="C356" s="3" t="s">
-        <v>1748</v>
-      </c>
-      <c r="D356" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="E356" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="F356" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G356" s="3" t="s">
-        <v>1749</v>
-      </c>
       <c r="H356" s="3" t="s">
-        <v>1750</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="357" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A357" s="3" t="s">
-        <v>1751</v>
+        <v>1753</v>
       </c>
       <c r="B357" s="3" t="s">
         <v>407</v>
       </c>
       <c r="C357" s="3" t="s">
-        <v>1752</v>
+        <v>1754</v>
       </c>
       <c r="D357" s="3" t="s">
-        <v>220</v>
+        <v>1755</v>
       </c>
       <c r="E357" s="3" t="s">
-        <v>1753</v>
+        <v>1756</v>
       </c>
       <c r="F357" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G357" s="3" t="s">
-        <v>1749</v>
+        <v>1757</v>
       </c>
       <c r="H357" s="3" t="s">
-        <v>436</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="358" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A358" s="3" t="s">
-        <v>1754</v>
+        <v>1759</v>
       </c>
       <c r="B358" s="3" t="s">
         <v>407</v>
       </c>
       <c r="C358" s="3" t="s">
-        <v>1755</v>
+        <v>1760</v>
       </c>
       <c r="D358" s="3" t="s">
-        <v>1756</v>
+        <v>1761</v>
       </c>
       <c r="E358" s="3" t="s">
-        <v>1757</v>
+        <v>1762</v>
       </c>
       <c r="F358" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G358" s="3" t="s">
-        <v>1758</v>
+        <v>1763</v>
       </c>
       <c r="H358" s="3" t="s">
-        <v>1759</v>
+        <v>15</v>
       </c>
     </row>
     <row r="359" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A359" s="3" t="s">
-        <v>1760</v>
+        <v>1764</v>
       </c>
       <c r="B359" s="3" t="s">
-        <v>671</v>
+        <v>407</v>
       </c>
       <c r="C359" s="3" t="s">
-        <v>1761</v>
+        <v>1765</v>
       </c>
       <c r="D359" s="3" t="s">
-        <v>1762</v>
+        <v>166</v>
       </c>
       <c r="E359" s="3" t="s">
-        <v>1763</v>
+        <v>420</v>
       </c>
       <c r="F359" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G359" s="3" t="s">
-        <v>1764</v>
+        <v>1766</v>
       </c>
       <c r="H359" s="3" t="s">
-        <v>15</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="360" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A360" s="3" t="s">
-        <v>1765</v>
+        <v>1768</v>
       </c>
       <c r="B360" s="3" t="s">
-        <v>572</v>
+        <v>407</v>
       </c>
       <c r="C360" s="3" t="s">
+        <v>1769</v>
+      </c>
+      <c r="D360" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="E360" s="3" t="s">
+        <v>1770</v>
+      </c>
+      <c r="F360" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G360" s="3" t="s">
         <v>1766</v>
       </c>
-      <c r="D360" s="3" t="s">
-        <v>1767</v>
-      </c>
-      <c r="E360" s="3" t="s">
-        <v>1768</v>
-      </c>
-      <c r="F360" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G360" s="3" t="s">
-        <v>1769</v>
-      </c>
       <c r="H360" s="3" t="s">
-        <v>15</v>
+        <v>436</v>
       </c>
     </row>
     <row r="361" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A361" s="3" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="B361" s="3" t="s">
-        <v>727</v>
+        <v>407</v>
       </c>
       <c r="C361" s="3" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="D361" s="3" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="E361" s="3" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="F361" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G361" s="3" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="H361" s="3" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="362" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A362" s="3" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="B362" s="3" t="s">
-        <v>551</v>
+        <v>671</v>
       </c>
       <c r="C362" s="3" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="D362" s="3" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="E362" s="3" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="F362" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G362" s="3" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="H362" s="3" t="s">
-        <v>1781</v>
+        <v>15</v>
       </c>
     </row>
     <row r="363" spans="1:8" x14ac:dyDescent="0.25">
@@ -16163,152 +16214,152 @@
         <v>1782</v>
       </c>
       <c r="B363" s="3" t="s">
-        <v>407</v>
+        <v>572</v>
       </c>
       <c r="C363" s="3" t="s">
         <v>1783</v>
       </c>
       <c r="D363" s="3" t="s">
-        <v>409</v>
+        <v>1784</v>
       </c>
       <c r="E363" s="3" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="F363" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G363" s="3" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="H363" s="3" t="s">
-        <v>251</v>
+        <v>15</v>
       </c>
     </row>
     <row r="364" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A364" s="3" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="B364" s="3" t="s">
-        <v>154</v>
+        <v>727</v>
       </c>
       <c r="C364" s="3" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="D364" s="3" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="E364" s="3" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="F364" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G364" s="3" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="H364" s="3" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="365" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A365" s="3" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="B365" s="3" t="s">
-        <v>407</v>
+        <v>551</v>
       </c>
       <c r="C365" s="3" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="D365" s="3" t="s">
-        <v>166</v>
+        <v>1795</v>
       </c>
       <c r="E365" s="3" t="s">
-        <v>1794</v>
+        <v>1796</v>
       </c>
       <c r="F365" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G365" s="3" t="s">
-        <v>1795</v>
+        <v>1797</v>
       </c>
       <c r="H365" s="3" t="s">
-        <v>15</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="366" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A366" s="3" t="s">
-        <v>1796</v>
+        <v>1799</v>
       </c>
       <c r="B366" s="3" t="s">
-        <v>572</v>
+        <v>407</v>
       </c>
       <c r="C366" s="3" t="s">
-        <v>1797</v>
+        <v>1800</v>
       </c>
       <c r="D366" s="3" t="s">
-        <v>1798</v>
+        <v>409</v>
       </c>
       <c r="E366" s="3" t="s">
-        <v>1799</v>
+        <v>1801</v>
       </c>
       <c r="F366" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G366" s="3" t="s">
-        <v>1800</v>
+        <v>1802</v>
       </c>
       <c r="H366" s="3" t="s">
-        <v>1801</v>
+        <v>251</v>
       </c>
     </row>
     <row r="367" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A367" s="3" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="B367" s="3" t="s">
-        <v>572</v>
+        <v>154</v>
       </c>
       <c r="C367" s="3" t="s">
-        <v>1797</v>
+        <v>1804</v>
       </c>
       <c r="D367" s="3" t="s">
-        <v>1803</v>
+        <v>1805</v>
       </c>
       <c r="E367" s="3" t="s">
-        <v>1804</v>
+        <v>1806</v>
       </c>
       <c r="F367" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G367" s="3" t="s">
-        <v>1800</v>
+        <v>1807</v>
       </c>
       <c r="H367" s="3" t="s">
-        <v>1801</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="368" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A368" s="3" t="s">
-        <v>1805</v>
+        <v>1809</v>
       </c>
       <c r="B368" s="3" t="s">
-        <v>572</v>
+        <v>407</v>
       </c>
       <c r="C368" s="3" t="s">
-        <v>1806</v>
+        <v>1810</v>
       </c>
       <c r="D368" s="3" t="s">
-        <v>1807</v>
+        <v>166</v>
       </c>
       <c r="E368" s="3" t="s">
-        <v>1808</v>
+        <v>1811</v>
       </c>
       <c r="F368" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G368" s="3" t="s">
-        <v>1809</v>
+        <v>1812</v>
       </c>
       <c r="H368" s="3" t="s">
         <v>15</v>
@@ -16316,77 +16367,77 @@
     </row>
     <row r="369" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A369" s="3" t="s">
-        <v>1810</v>
+        <v>1813</v>
       </c>
       <c r="B369" s="3" t="s">
         <v>572</v>
       </c>
       <c r="C369" s="3" t="s">
-        <v>1811</v>
+        <v>1814</v>
       </c>
       <c r="D369" s="3" t="s">
-        <v>1812</v>
+        <v>1815</v>
       </c>
       <c r="E369" s="3" t="s">
-        <v>1813</v>
+        <v>1816</v>
       </c>
       <c r="F369" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G369" s="3" t="s">
-        <v>1814</v>
+        <v>1817</v>
       </c>
       <c r="H369" s="3" t="s">
-        <v>1815</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="370" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A370" s="3" t="s">
-        <v>1816</v>
+        <v>1819</v>
       </c>
       <c r="B370" s="3" t="s">
         <v>572</v>
       </c>
       <c r="C370" s="3" t="s">
-        <v>1817</v>
+        <v>1814</v>
       </c>
       <c r="D370" s="3" t="s">
-        <v>1818</v>
+        <v>1820</v>
       </c>
       <c r="E370" s="3" t="s">
-        <v>1819</v>
+        <v>1821</v>
       </c>
       <c r="F370" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G370" s="3" t="s">
-        <v>1820</v>
+        <v>1817</v>
       </c>
       <c r="H370" s="3" t="s">
-        <v>15</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="371" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A371" s="3" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="B371" s="3" t="s">
         <v>572</v>
       </c>
       <c r="C371" s="3" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="D371" s="3" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="E371" s="3" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="F371" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G371" s="3" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="H371" s="3" t="s">
         <v>15</v>
@@ -16394,77 +16445,77 @@
     </row>
     <row r="372" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A372" s="3" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="B372" s="3" t="s">
-        <v>775</v>
+        <v>572</v>
       </c>
       <c r="C372" s="3" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="D372" s="3" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="E372" s="3" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="F372" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G372" s="3" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="H372" s="3" t="s">
-        <v>15</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="373" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A373" s="3" t="s">
-        <v>1831</v>
+        <v>1833</v>
       </c>
       <c r="B373" s="3" t="s">
-        <v>253</v>
+        <v>572</v>
       </c>
       <c r="C373" s="3" t="s">
-        <v>1832</v>
+        <v>1834</v>
       </c>
       <c r="D373" s="3" t="s">
-        <v>1833</v>
+        <v>1835</v>
       </c>
       <c r="E373" s="3" t="s">
-        <v>268</v>
+        <v>1836</v>
       </c>
       <c r="F373" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G373" s="3" t="s">
-        <v>1834</v>
+        <v>1837</v>
       </c>
       <c r="H373" s="3" t="s">
-        <v>269</v>
+        <v>15</v>
       </c>
     </row>
     <row r="374" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A374" s="3" t="s">
-        <v>1835</v>
+        <v>1838</v>
       </c>
       <c r="B374" s="3" t="s">
-        <v>253</v>
+        <v>572</v>
       </c>
       <c r="C374" s="3" t="s">
-        <v>1836</v>
+        <v>1839</v>
       </c>
       <c r="D374" s="3" t="s">
-        <v>1837</v>
+        <v>1840</v>
       </c>
       <c r="E374" s="3" t="s">
-        <v>1838</v>
+        <v>1841</v>
       </c>
       <c r="F374" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G374" s="3" t="s">
-        <v>1839</v>
+        <v>1842</v>
       </c>
       <c r="H374" s="3" t="s">
         <v>15</v>
@@ -16472,77 +16523,77 @@
     </row>
     <row r="375" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A375" s="3" t="s">
-        <v>1840</v>
+        <v>1843</v>
       </c>
       <c r="B375" s="3" t="s">
-        <v>750</v>
+        <v>775</v>
       </c>
       <c r="C375" s="3" t="s">
-        <v>1841</v>
+        <v>1844</v>
       </c>
       <c r="D375" s="3" t="s">
-        <v>1842</v>
+        <v>1845</v>
       </c>
       <c r="E375" s="3" t="s">
-        <v>763</v>
+        <v>1846</v>
       </c>
       <c r="F375" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G375" s="3" t="s">
-        <v>1843</v>
+        <v>1847</v>
       </c>
       <c r="H375" s="3" t="s">
-        <v>1844</v>
+        <v>15</v>
       </c>
     </row>
     <row r="376" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A376" s="3" t="s">
-        <v>1845</v>
+        <v>1848</v>
       </c>
       <c r="B376" s="3" t="s">
-        <v>407</v>
+        <v>253</v>
       </c>
       <c r="C376" s="3" t="s">
-        <v>1846</v>
+        <v>1849</v>
       </c>
       <c r="D376" s="3" t="s">
-        <v>1847</v>
+        <v>1850</v>
       </c>
       <c r="E376" s="3" t="s">
-        <v>1848</v>
+        <v>268</v>
       </c>
       <c r="F376" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G376" s="3" t="s">
-        <v>1849</v>
+        <v>1851</v>
       </c>
       <c r="H376" s="3" t="s">
-        <v>15</v>
+        <v>269</v>
       </c>
     </row>
     <row r="377" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A377" s="3" t="s">
-        <v>1850</v>
+        <v>1852</v>
       </c>
       <c r="B377" s="3" t="s">
-        <v>407</v>
+        <v>253</v>
       </c>
       <c r="C377" s="3" t="s">
-        <v>1851</v>
+        <v>1853</v>
       </c>
       <c r="D377" s="3" t="s">
-        <v>115</v>
+        <v>1854</v>
       </c>
       <c r="E377" s="3" t="s">
-        <v>1852</v>
+        <v>1855</v>
       </c>
       <c r="F377" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G377" s="3" t="s">
-        <v>1849</v>
+        <v>1856</v>
       </c>
       <c r="H377" s="3" t="s">
         <v>15</v>
@@ -16550,51 +16601,51 @@
     </row>
     <row r="378" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A378" s="3" t="s">
-        <v>1853</v>
+        <v>1857</v>
       </c>
       <c r="B378" s="3" t="s">
-        <v>671</v>
+        <v>750</v>
       </c>
       <c r="C378" s="3" t="s">
-        <v>1854</v>
+        <v>1858</v>
       </c>
       <c r="D378" s="3" t="s">
-        <v>1847</v>
+        <v>1859</v>
       </c>
       <c r="E378" s="3" t="s">
-        <v>1848</v>
+        <v>763</v>
       </c>
       <c r="F378" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G378" s="3" t="s">
-        <v>1849</v>
+        <v>1860</v>
       </c>
       <c r="H378" s="3" t="s">
-        <v>15</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="379" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A379" s="3" t="s">
-        <v>1855</v>
+        <v>1862</v>
       </c>
       <c r="B379" s="3" t="s">
-        <v>671</v>
+        <v>407</v>
       </c>
       <c r="C379" s="3" t="s">
-        <v>1856</v>
+        <v>1863</v>
       </c>
       <c r="D379" s="3" t="s">
-        <v>115</v>
+        <v>1864</v>
       </c>
       <c r="E379" s="3" t="s">
-        <v>1852</v>
+        <v>1865</v>
       </c>
       <c r="F379" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G379" s="3" t="s">
-        <v>1849</v>
+        <v>1866</v>
       </c>
       <c r="H379" s="3" t="s">
         <v>15</v>
@@ -16602,39 +16653,39 @@
     </row>
     <row r="380" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A380" s="3" t="s">
-        <v>1857</v>
+        <v>1867</v>
       </c>
       <c r="B380" s="3" t="s">
-        <v>671</v>
+        <v>407</v>
       </c>
       <c r="C380" s="3" t="s">
-        <v>1854</v>
+        <v>1868</v>
       </c>
       <c r="D380" s="3" t="s">
-        <v>1858</v>
+        <v>115</v>
       </c>
       <c r="E380" s="3" t="s">
-        <v>1859</v>
+        <v>1869</v>
       </c>
       <c r="F380" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G380" s="3" t="s">
-        <v>1860</v>
+        <v>1866</v>
       </c>
       <c r="H380" s="3" t="s">
-        <v>1861</v>
+        <v>15</v>
       </c>
     </row>
     <row r="381" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A381" s="3" t="s">
-        <v>1862</v>
+        <v>1870</v>
       </c>
       <c r="B381" s="3" t="s">
-        <v>344</v>
+        <v>671</v>
       </c>
       <c r="C381" s="3" t="s">
-        <v>1863</v>
+        <v>1871</v>
       </c>
       <c r="D381" s="3" t="s">
         <v>1864</v>
@@ -16654,25 +16705,25 @@
     </row>
     <row r="382" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A382" s="3" t="s">
-        <v>1867</v>
+        <v>1872</v>
       </c>
       <c r="B382" s="3" t="s">
-        <v>775</v>
+        <v>671</v>
       </c>
       <c r="C382" s="3" t="s">
-        <v>1868</v>
+        <v>1873</v>
       </c>
       <c r="D382" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E382" s="3" t="s">
         <v>1869</v>
-      </c>
-      <c r="E382" s="3" t="s">
-        <v>1870</v>
       </c>
       <c r="F382" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G382" s="3" t="s">
-        <v>1871</v>
+        <v>1866</v>
       </c>
       <c r="H382" s="3" t="s">
         <v>15</v>
@@ -16680,106 +16731,106 @@
     </row>
     <row r="383" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A383" s="3" t="s">
-        <v>1872</v>
+        <v>1874</v>
       </c>
       <c r="B383" s="3" t="s">
-        <v>775</v>
+        <v>671</v>
       </c>
       <c r="C383" s="3" t="s">
-        <v>1873</v>
+        <v>1871</v>
       </c>
       <c r="D383" s="3" t="s">
-        <v>1869</v>
+        <v>1875</v>
       </c>
       <c r="E383" s="3" t="s">
-        <v>1874</v>
+        <v>1876</v>
       </c>
       <c r="F383" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G383" s="3" t="s">
-        <v>1871</v>
+        <v>1877</v>
       </c>
       <c r="H383" s="3" t="s">
-        <v>15</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="384" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A384" s="3" t="s">
-        <v>1875</v>
+        <v>1879</v>
       </c>
       <c r="B384" s="3" t="s">
-        <v>775</v>
+        <v>344</v>
       </c>
       <c r="C384" s="3" t="s">
-        <v>1876</v>
+        <v>1880</v>
       </c>
       <c r="D384" s="3" t="s">
-        <v>631</v>
+        <v>1881</v>
       </c>
       <c r="E384" s="3" t="s">
-        <v>1877</v>
+        <v>1882</v>
       </c>
       <c r="F384" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G384" s="3" t="s">
-        <v>1878</v>
+        <v>1883</v>
       </c>
       <c r="H384" s="3" t="s">
-        <v>1879</v>
+        <v>15</v>
       </c>
     </row>
     <row r="385" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A385" s="3" t="s">
-        <v>1880</v>
+        <v>1884</v>
       </c>
       <c r="B385" s="3" t="s">
-        <v>572</v>
+        <v>775</v>
       </c>
       <c r="C385" s="3" t="s">
-        <v>1881</v>
+        <v>1885</v>
       </c>
       <c r="D385" s="3" t="s">
-        <v>1882</v>
+        <v>1886</v>
       </c>
       <c r="E385" s="3" t="s">
-        <v>1883</v>
+        <v>1887</v>
       </c>
       <c r="F385" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G385" s="3" t="s">
-        <v>1884</v>
+        <v>1888</v>
       </c>
       <c r="H385" s="3" t="s">
-        <v>1885</v>
+        <v>15</v>
       </c>
     </row>
     <row r="386" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A386" s="3" t="s">
+        <v>1889</v>
+      </c>
+      <c r="B386" s="3" t="s">
+        <v>775</v>
+      </c>
+      <c r="C386" s="3" t="s">
+        <v>1890</v>
+      </c>
+      <c r="D386" s="3" t="s">
         <v>1886</v>
       </c>
-      <c r="B386" s="3" t="s">
-        <v>1090</v>
-      </c>
-      <c r="C386" s="3" t="s">
-        <v>1887</v>
-      </c>
-      <c r="D386" s="3" t="s">
-        <v>1888</v>
-      </c>
       <c r="E386" s="3" t="s">
-        <v>1889</v>
+        <v>1891</v>
       </c>
       <c r="F386" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G386" s="3" t="s">
-        <v>1890</v>
+        <v>1888</v>
       </c>
       <c r="H386" s="3" t="s">
-        <v>1891</v>
+        <v>15</v>
       </c>
     </row>
     <row r="387" spans="1:8" x14ac:dyDescent="0.25">
@@ -16787,25 +16838,25 @@
         <v>1892</v>
       </c>
       <c r="B387" s="3" t="s">
-        <v>198</v>
+        <v>775</v>
       </c>
       <c r="C387" s="3" t="s">
         <v>1893</v>
       </c>
       <c r="D387" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="E387" s="3" t="s">
         <v>1894</v>
       </c>
-      <c r="E387" s="3" t="s">
+      <c r="F387" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G387" s="3" t="s">
         <v>1895</v>
       </c>
-      <c r="F387" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G387" s="3" t="s">
+      <c r="H387" s="3" t="s">
         <v>1896</v>
-      </c>
-      <c r="H387" s="3" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="388" spans="1:8" x14ac:dyDescent="0.25">
@@ -16813,7 +16864,7 @@
         <v>1897</v>
       </c>
       <c r="B388" s="3" t="s">
-        <v>198</v>
+        <v>572</v>
       </c>
       <c r="C388" s="3" t="s">
         <v>1898</v>
@@ -16831,85 +16882,85 @@
         <v>1901</v>
       </c>
       <c r="H388" s="3" t="s">
-        <v>15</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="389" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A389" s="3" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
       <c r="B389" s="3" t="s">
-        <v>750</v>
+        <v>1107</v>
       </c>
       <c r="C389" s="3" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="D389" s="3" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
       <c r="E389" s="3" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
       <c r="F389" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G389" s="3" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="H389" s="3" t="s">
-        <v>15</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="390" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A390" s="3" t="s">
-        <v>1907</v>
+        <v>1909</v>
       </c>
       <c r="B390" s="3" t="s">
-        <v>253</v>
+        <v>198</v>
       </c>
       <c r="C390" s="3" t="s">
-        <v>1908</v>
+        <v>1910</v>
       </c>
       <c r="D390" s="3" t="s">
-        <v>1909</v>
+        <v>1911</v>
       </c>
       <c r="E390" s="3" t="s">
-        <v>1910</v>
+        <v>1912</v>
       </c>
       <c r="F390" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G390" s="3" t="s">
-        <v>1911</v>
+        <v>1913</v>
       </c>
       <c r="H390" s="3" t="s">
-        <v>1912</v>
+        <v>15</v>
       </c>
     </row>
     <row r="391" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A391" s="3" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="B391" s="3" t="s">
-        <v>775</v>
+        <v>198</v>
       </c>
       <c r="C391" s="3" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="D391" s="3" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="E391" s="3" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="F391" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G391" s="3" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="H391" s="3" t="s">
-        <v>1918</v>
+        <v>15</v>
       </c>
     </row>
     <row r="392" spans="1:8" x14ac:dyDescent="0.25">
@@ -16917,7 +16968,7 @@
         <v>1919</v>
       </c>
       <c r="B392" s="3" t="s">
-        <v>48</v>
+        <v>750</v>
       </c>
       <c r="C392" s="3" t="s">
         <v>1920</v>
@@ -16929,7 +16980,7 @@
         <v>1922</v>
       </c>
       <c r="F392" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G392" s="3" t="s">
         <v>1923</v>
@@ -16943,51 +16994,51 @@
         <v>1924</v>
       </c>
       <c r="B393" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C393" s="3" t="s">
         <v>1925</v>
       </c>
-      <c r="C393" s="3" t="s">
+      <c r="D393" s="3" t="s">
         <v>1926</v>
       </c>
-      <c r="D393" s="3" t="s">
+      <c r="E393" s="3" t="s">
         <v>1927</v>
       </c>
-      <c r="E393" s="3" t="s">
+      <c r="F393" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G393" s="3" t="s">
         <v>1928</v>
       </c>
-      <c r="F393" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G393" s="3" t="s">
+      <c r="H393" s="3" t="s">
         <v>1929</v>
-      </c>
-      <c r="H393" s="3" t="s">
-        <v>1930</v>
       </c>
     </row>
     <row r="394" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A394" s="3" t="s">
+        <v>1930</v>
+      </c>
+      <c r="B394" s="3" t="s">
+        <v>775</v>
+      </c>
+      <c r="C394" s="3" t="s">
         <v>1931</v>
       </c>
-      <c r="B394" s="3" t="s">
-        <v>1925</v>
-      </c>
-      <c r="C394" s="3" t="s">
+      <c r="D394" s="3" t="s">
         <v>1932</v>
       </c>
-      <c r="D394" s="3" t="s">
+      <c r="E394" s="3" t="s">
         <v>1933</v>
-      </c>
-      <c r="E394" s="3" t="s">
-        <v>1934</v>
       </c>
       <c r="F394" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G394" s="3" t="s">
+        <v>1934</v>
+      </c>
+      <c r="H394" s="3" t="s">
         <v>1935</v>
-      </c>
-      <c r="H394" s="3" t="s">
-        <v>1930</v>
       </c>
     </row>
     <row r="395" spans="1:8" x14ac:dyDescent="0.25">
@@ -16995,7 +17046,7 @@
         <v>1936</v>
       </c>
       <c r="B395" s="3" t="s">
-        <v>1925</v>
+        <v>48</v>
       </c>
       <c r="C395" s="3" t="s">
         <v>1937</v>
@@ -17013,142 +17064,142 @@
         <v>1940</v>
       </c>
       <c r="H395" s="3" t="s">
-        <v>1941</v>
+        <v>15</v>
       </c>
     </row>
     <row r="396" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A396" s="3" t="s">
+        <v>1941</v>
+      </c>
+      <c r="B396" s="3" t="s">
         <v>1942</v>
       </c>
-      <c r="B396" s="3" t="s">
-        <v>344</v>
-      </c>
       <c r="C396" s="3" t="s">
-        <v>958</v>
+        <v>1943</v>
       </c>
       <c r="D396" s="3" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="E396" s="3" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="F396" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G396" s="3" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="H396" s="3" t="s">
-        <v>1946</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="397" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A397" s="3" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B397" s="3" t="s">
+        <v>1942</v>
+      </c>
+      <c r="C397" s="3" t="s">
+        <v>1949</v>
+      </c>
+      <c r="D397" s="3" t="s">
+        <v>1950</v>
+      </c>
+      <c r="E397" s="3" t="s">
+        <v>1951</v>
+      </c>
+      <c r="F397" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G397" s="3" t="s">
+        <v>1952</v>
+      </c>
+      <c r="H397" s="3" t="s">
         <v>1947</v>
-      </c>
-      <c r="B397" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="C397" s="3" t="s">
-        <v>1948</v>
-      </c>
-      <c r="D397" s="3" t="s">
-        <v>1949</v>
-      </c>
-      <c r="E397" s="3" t="s">
-        <v>1950</v>
-      </c>
-      <c r="F397" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G397" s="3" t="s">
-        <v>1951</v>
-      </c>
-      <c r="H397" s="3" t="s">
-        <v>1946</v>
       </c>
     </row>
     <row r="398" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A398" s="3" t="s">
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="B398" s="3" t="s">
-        <v>344</v>
+        <v>1942</v>
       </c>
       <c r="C398" s="3" t="s">
-        <v>1948</v>
+        <v>1954</v>
       </c>
       <c r="D398" s="3" t="s">
-        <v>1953</v>
+        <v>1955</v>
       </c>
       <c r="E398" s="3" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="F398" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G398" s="3" t="s">
-        <v>1951</v>
+        <v>1957</v>
       </c>
       <c r="H398" s="3" t="s">
-        <v>1946</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="399" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A399" s="3" t="s">
-        <v>1955</v>
+        <v>1959</v>
       </c>
       <c r="B399" s="3" t="s">
         <v>344</v>
       </c>
       <c r="C399" s="3" t="s">
-        <v>1948</v>
+        <v>958</v>
       </c>
       <c r="D399" s="3" t="s">
-        <v>1956</v>
+        <v>1960</v>
       </c>
       <c r="E399" s="3" t="s">
-        <v>1957</v>
+        <v>1961</v>
       </c>
       <c r="F399" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G399" s="3" t="s">
-        <v>1958</v>
+        <v>1962</v>
       </c>
       <c r="H399" s="3" t="s">
-        <v>15</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="400" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A400" s="3" t="s">
-        <v>1959</v>
+        <v>1964</v>
       </c>
       <c r="B400" s="3" t="s">
         <v>344</v>
       </c>
       <c r="C400" s="3" t="s">
-        <v>1960</v>
+        <v>1965</v>
       </c>
       <c r="D400" s="3" t="s">
-        <v>1961</v>
+        <v>1966</v>
       </c>
       <c r="E400" s="3" t="s">
-        <v>1962</v>
+        <v>1967</v>
       </c>
       <c r="F400" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G400" s="3" t="s">
+        <v>1968</v>
+      </c>
+      <c r="H400" s="3" t="s">
         <v>1963</v>
-      </c>
-      <c r="H400" s="3" t="s">
-        <v>1946</v>
       </c>
     </row>
     <row r="401" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A401" s="3" t="s">
-        <v>1964</v>
+        <v>1969</v>
       </c>
       <c r="B401" s="3" t="s">
         <v>344</v>
@@ -17157,10 +17208,10 @@
         <v>1965</v>
       </c>
       <c r="D401" s="3" t="s">
-        <v>1966</v>
+        <v>1970</v>
       </c>
       <c r="E401" s="3" t="s">
-        <v>1967</v>
+        <v>1971</v>
       </c>
       <c r="F401" s="3" t="s">
         <v>20</v>
@@ -17169,33 +17220,33 @@
         <v>1968</v>
       </c>
       <c r="H401" s="3" t="s">
-        <v>1969</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="402" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A402" s="3" t="s">
-        <v>1970</v>
+        <v>1972</v>
       </c>
       <c r="B402" s="3" t="s">
         <v>344</v>
       </c>
       <c r="C402" s="3" t="s">
-        <v>1971</v>
+        <v>1965</v>
       </c>
       <c r="D402" s="3" t="s">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="E402" s="3" t="s">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="F402" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G402" s="3" t="s">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="H402" s="3" t="s">
-        <v>1975</v>
+        <v>15</v>
       </c>
     </row>
     <row r="403" spans="1:8" x14ac:dyDescent="0.25">
@@ -17203,25 +17254,25 @@
         <v>1976</v>
       </c>
       <c r="B403" s="3" t="s">
-        <v>253</v>
+        <v>344</v>
       </c>
       <c r="C403" s="3" t="s">
         <v>1977</v>
       </c>
       <c r="D403" s="3" t="s">
-        <v>1949</v>
+        <v>1978</v>
       </c>
       <c r="E403" s="3" t="s">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="F403" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G403" s="3" t="s">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="H403" s="3" t="s">
-        <v>1980</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="404" spans="1:8" x14ac:dyDescent="0.25">
@@ -17229,7 +17280,7 @@
         <v>1981</v>
       </c>
       <c r="B404" s="3" t="s">
-        <v>253</v>
+        <v>344</v>
       </c>
       <c r="C404" s="3" t="s">
         <v>1982</v>
@@ -17244,244 +17295,244 @@
         <v>20</v>
       </c>
       <c r="G404" s="3" t="s">
-        <v>1979</v>
+        <v>1985</v>
       </c>
       <c r="H404" s="3" t="s">
-        <v>1946</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="405" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A405" s="3" t="s">
-        <v>1985</v>
+        <v>1987</v>
       </c>
       <c r="B405" s="3" t="s">
         <v>344</v>
       </c>
       <c r="C405" s="3" t="s">
-        <v>1986</v>
+        <v>1988</v>
       </c>
       <c r="D405" s="3" t="s">
-        <v>1987</v>
+        <v>1989</v>
       </c>
       <c r="E405" s="3" t="s">
-        <v>1988</v>
+        <v>1990</v>
       </c>
       <c r="F405" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G405" s="3" t="s">
-        <v>1989</v>
+        <v>1991</v>
       </c>
       <c r="H405" s="3" t="s">
-        <v>1990</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="406" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A406" s="3" t="s">
-        <v>1991</v>
+        <v>1993</v>
       </c>
       <c r="B406" s="3" t="s">
-        <v>344</v>
+        <v>253</v>
       </c>
       <c r="C406" s="3" t="s">
-        <v>1992</v>
+        <v>1994</v>
       </c>
       <c r="D406" s="3" t="s">
-        <v>1993</v>
+        <v>1966</v>
       </c>
       <c r="E406" s="3" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="F406" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G406" s="3" t="s">
-        <v>1989</v>
+        <v>1996</v>
       </c>
       <c r="H406" s="3" t="s">
-        <v>1946</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="407" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A407" s="3" t="s">
-        <v>1995</v>
+        <v>1998</v>
       </c>
       <c r="B407" s="3" t="s">
-        <v>344</v>
+        <v>253</v>
       </c>
       <c r="C407" s="3" t="s">
-        <v>964</v>
+        <v>1999</v>
       </c>
       <c r="D407" s="3" t="s">
+        <v>2000</v>
+      </c>
+      <c r="E407" s="3" t="s">
+        <v>2001</v>
+      </c>
+      <c r="F407" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G407" s="3" t="s">
         <v>1996</v>
       </c>
-      <c r="E407" s="3" t="s">
-        <v>1997</v>
-      </c>
-      <c r="F407" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G407" s="3" t="s">
-        <v>1989</v>
-      </c>
       <c r="H407" s="3" t="s">
-        <v>1946</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="408" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A408" s="3" t="s">
-        <v>1998</v>
+        <v>2002</v>
       </c>
       <c r="B408" s="3" t="s">
         <v>344</v>
       </c>
       <c r="C408" s="3" t="s">
-        <v>964</v>
+        <v>2003</v>
       </c>
       <c r="D408" s="3" t="s">
-        <v>1999</v>
+        <v>2004</v>
       </c>
       <c r="E408" s="3" t="s">
-        <v>2000</v>
+        <v>2005</v>
       </c>
       <c r="F408" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G408" s="3" t="s">
-        <v>1989</v>
+        <v>2006</v>
       </c>
       <c r="H408" s="3" t="s">
-        <v>1946</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="409" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A409" s="3" t="s">
-        <v>2001</v>
+        <v>2008</v>
       </c>
       <c r="B409" s="3" t="s">
-        <v>572</v>
+        <v>344</v>
       </c>
       <c r="C409" s="3" t="s">
-        <v>645</v>
+        <v>2009</v>
       </c>
       <c r="D409" s="3" t="s">
-        <v>2002</v>
+        <v>2010</v>
       </c>
       <c r="E409" s="3" t="s">
-        <v>2003</v>
+        <v>2011</v>
       </c>
       <c r="F409" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G409" s="3" t="s">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="H409" s="3" t="s">
-        <v>2005</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="410" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A410" s="3" t="s">
+        <v>2012</v>
+      </c>
+      <c r="B410" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C410" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="D410" s="3" t="s">
+        <v>2013</v>
+      </c>
+      <c r="E410" s="3" t="s">
+        <v>2014</v>
+      </c>
+      <c r="F410" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G410" s="3" t="s">
         <v>2006</v>
       </c>
-      <c r="B410" s="3" t="s">
-        <v>572</v>
-      </c>
-      <c r="C410" s="3" t="s">
-        <v>2007</v>
-      </c>
-      <c r="D410" s="3" t="s">
-        <v>2008</v>
-      </c>
-      <c r="E410" s="3" t="s">
-        <v>2009</v>
-      </c>
-      <c r="F410" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G410" s="3" t="s">
-        <v>2010</v>
-      </c>
       <c r="H410" s="3" t="s">
-        <v>2005</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="411" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A411" s="3" t="s">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="B411" s="3" t="s">
-        <v>572</v>
+        <v>344</v>
       </c>
       <c r="C411" s="3" t="s">
-        <v>2007</v>
+        <v>964</v>
       </c>
       <c r="D411" s="3" t="s">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="E411" s="3" t="s">
-        <v>2013</v>
+        <v>2017</v>
       </c>
       <c r="F411" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G411" s="3" t="s">
-        <v>2014</v>
+        <v>2006</v>
       </c>
       <c r="H411" s="3" t="s">
-        <v>2015</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="412" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A412" s="3" t="s">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="B412" s="3" t="s">
         <v>572</v>
       </c>
       <c r="C412" s="3" t="s">
-        <v>2017</v>
+        <v>645</v>
       </c>
       <c r="D412" s="3" t="s">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="E412" s="3" t="s">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="F412" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G412" s="3" t="s">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="H412" s="3" t="s">
-        <v>2021</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="413" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A413" s="3" t="s">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B413" s="3" t="s">
         <v>572</v>
       </c>
       <c r="C413" s="3" t="s">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D413" s="3" t="s">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E413" s="3" t="s">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F413" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G413" s="3" t="s">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="H413" s="3" t="s">
-        <v>2027</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="414" spans="1:8" x14ac:dyDescent="0.25">
@@ -17489,25 +17540,25 @@
         <v>2028</v>
       </c>
       <c r="B414" s="3" t="s">
-        <v>750</v>
+        <v>572</v>
       </c>
       <c r="C414" s="3" t="s">
+        <v>2024</v>
+      </c>
+      <c r="D414" s="3" t="s">
         <v>2029</v>
       </c>
-      <c r="D414" s="3" t="s">
+      <c r="E414" s="3" t="s">
         <v>2030</v>
       </c>
-      <c r="E414" s="3" t="s">
+      <c r="F414" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G414" s="3" t="s">
         <v>2031</v>
       </c>
-      <c r="F414" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G414" s="3" t="s">
+      <c r="H414" s="3" t="s">
         <v>2032</v>
-      </c>
-      <c r="H414" s="3" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="415" spans="1:8" x14ac:dyDescent="0.25">
@@ -17527,7 +17578,7 @@
         <v>2036</v>
       </c>
       <c r="F415" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G415" s="3" t="s">
         <v>2037</v>
@@ -17541,7 +17592,7 @@
         <v>2039</v>
       </c>
       <c r="B416" s="3" t="s">
-        <v>253</v>
+        <v>572</v>
       </c>
       <c r="C416" s="3" t="s">
         <v>2040</v>
@@ -17559,33 +17610,33 @@
         <v>2043</v>
       </c>
       <c r="H416" s="3" t="s">
-        <v>15</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="417" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A417" s="3" t="s">
-        <v>2044</v>
+        <v>2045</v>
       </c>
       <c r="B417" s="3" t="s">
-        <v>572</v>
+        <v>750</v>
       </c>
       <c r="C417" s="3" t="s">
-        <v>2045</v>
+        <v>2046</v>
       </c>
       <c r="D417" s="3" t="s">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="E417" s="3" t="s">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="F417" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G417" s="3" t="s">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="H417" s="3" t="s">
-        <v>2049</v>
+        <v>15</v>
       </c>
     </row>
     <row r="418" spans="1:8" x14ac:dyDescent="0.25">
@@ -17593,7 +17644,7 @@
         <v>2050</v>
       </c>
       <c r="B418" s="3" t="s">
-        <v>253</v>
+        <v>572</v>
       </c>
       <c r="C418" s="3" t="s">
         <v>2051</v>
@@ -17605,36 +17656,36 @@
         <v>2053</v>
       </c>
       <c r="F418" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G418" s="3" t="s">
         <v>2054</v>
       </c>
       <c r="H418" s="3" t="s">
-        <v>2049</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="419" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A419" s="3" t="s">
-        <v>2055</v>
+        <v>2056</v>
       </c>
       <c r="B419" s="3" t="s">
         <v>253</v>
       </c>
       <c r="C419" s="3" t="s">
-        <v>2056</v>
+        <v>2057</v>
       </c>
       <c r="D419" s="3" t="s">
-        <v>2057</v>
+        <v>2058</v>
       </c>
       <c r="E419" s="3" t="s">
-        <v>2058</v>
+        <v>2059</v>
       </c>
       <c r="F419" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G419" s="3" t="s">
-        <v>2059</v>
+        <v>2060</v>
       </c>
       <c r="H419" s="3" t="s">
         <v>15</v>
@@ -17642,184 +17693,262 @@
     </row>
     <row r="420" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A420" s="3" t="s">
-        <v>2060</v>
+        <v>2061</v>
       </c>
       <c r="B420" s="3" t="s">
-        <v>253</v>
+        <v>572</v>
       </c>
       <c r="C420" s="3" t="s">
-        <v>2061</v>
+        <v>2062</v>
       </c>
       <c r="D420" s="3" t="s">
-        <v>959</v>
+        <v>2063</v>
       </c>
       <c r="E420" s="3" t="s">
-        <v>2062</v>
+        <v>2064</v>
       </c>
       <c r="F420" s="3" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G420" s="3" t="s">
-        <v>2063</v>
+        <v>2065</v>
       </c>
       <c r="H420" s="3" t="s">
-        <v>2049</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="421" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A421" s="3" t="s">
-        <v>2064</v>
+        <v>2067</v>
       </c>
       <c r="B421" s="3" t="s">
         <v>253</v>
       </c>
       <c r="C421" s="3" t="s">
-        <v>2051</v>
+        <v>2068</v>
       </c>
       <c r="D421" s="3" t="s">
-        <v>2065</v>
+        <v>2069</v>
       </c>
       <c r="E421" s="3" t="s">
+        <v>2070</v>
+      </c>
+      <c r="F421" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G421" s="3" t="s">
+        <v>2071</v>
+      </c>
+      <c r="H421" s="3" t="s">
         <v>2066</v>
-      </c>
-      <c r="F421" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G421" s="3" t="s">
-        <v>2067</v>
-      </c>
-      <c r="H421" s="3" t="s">
-        <v>2068</v>
       </c>
     </row>
     <row r="422" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A422" s="3" t="s">
-        <v>2069</v>
+        <v>2072</v>
       </c>
       <c r="B422" s="3" t="s">
         <v>253</v>
       </c>
       <c r="C422" s="3" t="s">
-        <v>2070</v>
+        <v>2073</v>
       </c>
       <c r="D422" s="3" t="s">
-        <v>166</v>
+        <v>2074</v>
       </c>
       <c r="E422" s="3" t="s">
-        <v>2071</v>
+        <v>2075</v>
       </c>
       <c r="F422" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G422" s="3" t="s">
-        <v>2067</v>
+        <v>2076</v>
       </c>
       <c r="H422" s="3" t="s">
-        <v>2049</v>
+        <v>15</v>
       </c>
     </row>
     <row r="423" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A423" s="3" t="s">
-        <v>2072</v>
+        <v>2077</v>
       </c>
       <c r="B423" s="3" t="s">
         <v>253</v>
       </c>
       <c r="C423" s="3" t="s">
-        <v>2073</v>
+        <v>2078</v>
       </c>
       <c r="D423" s="3" t="s">
-        <v>2074</v>
+        <v>959</v>
       </c>
       <c r="E423" s="3" t="s">
-        <v>2075</v>
+        <v>2079</v>
       </c>
       <c r="F423" s="3" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="G423" s="3" t="s">
-        <v>2067</v>
+        <v>2080</v>
       </c>
       <c r="H423" s="3" t="s">
-        <v>2049</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="424" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A424" s="3" t="s">
-        <v>2076</v>
+        <v>2081</v>
       </c>
       <c r="B424" s="3" t="s">
         <v>253</v>
       </c>
       <c r="C424" s="3" t="s">
-        <v>2077</v>
+        <v>2068</v>
       </c>
       <c r="D424" s="3" t="s">
-        <v>959</v>
+        <v>2082</v>
       </c>
       <c r="E424" s="3" t="s">
-        <v>2078</v>
+        <v>2083</v>
       </c>
       <c r="F424" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G424" s="3" t="s">
-        <v>2067</v>
+        <v>2084</v>
       </c>
       <c r="H424" s="3" t="s">
-        <v>2049</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="425" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A425" s="3" t="s">
-        <v>2079</v>
+        <v>2086</v>
       </c>
       <c r="B425" s="3" t="s">
-        <v>344</v>
+        <v>253</v>
       </c>
       <c r="C425" s="3" t="s">
-        <v>2080</v>
+        <v>2087</v>
       </c>
       <c r="D425" s="3" t="s">
-        <v>2081</v>
+        <v>166</v>
       </c>
       <c r="E425" s="3" t="s">
-        <v>2082</v>
+        <v>2088</v>
       </c>
       <c r="F425" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G425" s="3" t="s">
-        <v>2083</v>
+        <v>2084</v>
       </c>
       <c r="H425" s="3" t="s">
-        <v>2084</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="426" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A426" s="3" t="s">
-        <v>2085</v>
+        <v>2089</v>
       </c>
       <c r="B426" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C426" s="3" t="s">
+        <v>2090</v>
+      </c>
+      <c r="D426" s="3" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E426" s="3" t="s">
+        <v>2092</v>
+      </c>
+      <c r="F426" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G426" s="3" t="s">
+        <v>2084</v>
+      </c>
+      <c r="H426" s="3" t="s">
+        <v>2066</v>
+      </c>
+    </row>
+    <row r="427" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A427" s="3" t="s">
+        <v>2093</v>
+      </c>
+      <c r="B427" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C427" s="3" t="s">
+        <v>2094</v>
+      </c>
+      <c r="D427" s="3" t="s">
+        <v>959</v>
+      </c>
+      <c r="E427" s="3" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F427" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G427" s="3" t="s">
+        <v>2084</v>
+      </c>
+      <c r="H427" s="3" t="s">
+        <v>2066</v>
+      </c>
+    </row>
+    <row r="428" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A428" s="3" t="s">
+        <v>2096</v>
+      </c>
+      <c r="B428" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C428" s="3" t="s">
+        <v>2097</v>
+      </c>
+      <c r="D428" s="3" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E428" s="3" t="s">
+        <v>2099</v>
+      </c>
+      <c r="F428" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G428" s="3" t="s">
+        <v>2100</v>
+      </c>
+      <c r="H428" s="3" t="s">
+        <v>2101</v>
+      </c>
+    </row>
+    <row r="429" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A429" s="3" t="s">
+        <v>2102</v>
+      </c>
+      <c r="B429" s="3" t="s">
         <v>551</v>
       </c>
-      <c r="C426" s="3" t="s">
-        <v>2086</v>
-      </c>
-      <c r="D426" s="3" t="s">
-        <v>2087</v>
-      </c>
-      <c r="E426" s="3" t="s">
-        <v>2088</v>
-      </c>
-      <c r="F426" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G426" s="3" t="s">
-        <v>2089</v>
-      </c>
-      <c r="H426" s="3" t="s">
-        <v>2090</v>
+      <c r="C429" s="3" t="s">
+        <v>2103</v>
+      </c>
+      <c r="D429" s="3" t="s">
+        <v>2104</v>
+      </c>
+      <c r="E429" s="3" t="s">
+        <v>2105</v>
+      </c>
+      <c r="F429" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G429" s="3" t="s">
+        <v>2106</v>
+      </c>
+      <c r="H429" s="3" t="s">
+        <v>2107</v>
       </c>
     </row>
   </sheetData>
@@ -17840,82 +17969,82 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>2091</v>
+        <v>2108</v>
       </c>
       <c r="B1" t="s">
-        <v>2092</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>2093</v>
+        <v>2110</v>
       </c>
       <c r="B2" t="s">
-        <v>2094</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>2095</v>
+        <v>2112</v>
       </c>
       <c r="B3" t="s">
-        <v>2096</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>2097</v>
+        <v>2114</v>
       </c>
       <c r="B4" t="s">
-        <v>2098</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>2099</v>
+        <v>2116</v>
       </c>
       <c r="B5" t="s">
-        <v>2100</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>2101</v>
+        <v>2118</v>
       </c>
       <c r="B6" t="s">
-        <v>2102</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>2103</v>
+        <v>2120</v>
       </c>
       <c r="B7" t="s">
-        <v>2104</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>2105</v>
+        <v>2122</v>
       </c>
       <c r="B8" t="s">
-        <v>2106</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>2105</v>
+        <v>2122</v>
       </c>
       <c r="B9" t="s">
-        <v>2107</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>2105</v>
+        <v>2122</v>
       </c>
       <c r="B10" t="s">
-        <v>2108</v>
+        <v>2125</v>
       </c>
     </row>
   </sheetData>
